--- a/Scout/johnston-vs-waukee-082826.xlsx
+++ b/Scout/johnston-vs-waukee-082826.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zcalv\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA5A733-2817-4BC6-9AC8-147745F191DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R265283d335384935"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0">
   <si>
     <t>PLAY #</t>
   </si>
@@ -55,6 +46,9 @@
     <t>EFF</t>
   </si>
   <si>
+    <t>MEN IN BOX</t>
+  </si>
+  <si>
     <t>GAP</t>
   </si>
   <si>
@@ -73,6 +67,9 @@
     <t>OFF STR</t>
   </si>
   <si>
+    <t>OFF FORM</t>
+  </si>
+  <si>
     <t>OFF PLAY</t>
   </si>
   <si>
@@ -82,9 +79,15 @@
     <t>MOTION DIR</t>
   </si>
   <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
     <t>SERIES</t>
   </si>
   <si>
+    <t>PEN YARDS</t>
+  </si>
+  <si>
     <t>K</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>BAL</t>
   </si>
   <si>
+    <t>ACE</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
@@ -124,6 +130,9 @@
     <t>Complete</t>
   </si>
   <si>
+    <t>TRIPS</t>
+  </si>
+  <si>
     <t>Punt Rec</t>
   </si>
   <si>
@@ -139,9 +148,15 @@
     <t>N</t>
   </si>
   <si>
+    <t>Y OFF TRIPS</t>
+  </si>
+  <si>
     <t>SLANT</t>
   </si>
   <si>
+    <t>TRIPS TIGHT BUNCH</t>
+  </si>
+  <si>
     <t>BUBBLE</t>
   </si>
   <si>
@@ -163,6 +178,9 @@
     <t>STICK</t>
   </si>
   <si>
+    <t>Y OFF TRIPS PRO</t>
+  </si>
+  <si>
     <t>GIVE @ 2</t>
   </si>
   <si>
@@ -172,6 +190,9 @@
     <t>E-Alley</t>
   </si>
   <si>
+    <t>Y OFF PRO</t>
+  </si>
+  <si>
     <t>BUCK</t>
   </si>
   <si>
@@ -187,6 +208,9 @@
     <t>LEVELS</t>
   </si>
   <si>
+    <t>TRIPS PRO</t>
+  </si>
+  <si>
     <t>HB SCREEN</t>
   </si>
   <si>
@@ -202,6 +226,9 @@
     <t>TOSS</t>
   </si>
   <si>
+    <t>TWINS Y OFF OPEN</t>
+  </si>
+  <si>
     <t>Sack</t>
   </si>
   <si>
@@ -235,7 +262,13 @@
     <t>POWER</t>
   </si>
   <si>
+    <t>TWINS WING</t>
+  </si>
+  <si>
     <t>Return</t>
+  </si>
+  <si>
+    <t>FAR</t>
   </si>
   <si>
     <t>Complete, TD</t>
@@ -267,889 +300,11 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U123"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" customWidth="1"/>
-    <col min="20" max="20" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.36328125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:Y123"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1213,8 +368,20 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1222,22 +389,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1245,7 +412,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1257,39 +424,42 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
-      </c>
-      <c r="S3" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1301,34 +471,37 @@
         <v>-22</v>
       </c>
       <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>-5</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>33</v>
       </c>
       <c r="S4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T4" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="U4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1336,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1348,34 +521,34 @@
         <v>-17</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T5" t="s">
-        <v>31</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>33</v>
+      </c>
+      <c r="U5" t="s">
+        <v>35</v>
+      </c>
+      <c r="V5" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1383,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1395,31 +568,34 @@
         <v>-16</v>
       </c>
       <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
       </c>
       <c r="S6" t="s">
-        <v>31</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1427,7 +603,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -1439,22 +615,22 @@
         <v>-17</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7">
+        <v>41</v>
+      </c>
+      <c r="P7">
         <v>38</v>
       </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="X7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1462,7 +638,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1474,43 +650,46 @@
         <v>-45</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8">
+        <v>44</v>
+      </c>
+      <c r="N8">
         <v>11</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>4</v>
       </c>
-      <c r="Q8" t="s">
-        <v>30</v>
-      </c>
       <c r="R8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T8" t="s">
-        <v>30</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="U8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1518,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1530,40 +709,43 @@
         <v>-45</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9">
+        <v>44</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>30</v>
+      <c r="O9">
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S9" t="s">
-        <v>30</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="T9" t="s">
+        <v>48</v>
+      </c>
+      <c r="U9" t="s">
+        <v>35</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1571,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -1583,43 +765,46 @@
         <v>-49</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J10">
         <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10">
+        <v>32</v>
+      </c>
+      <c r="N10">
         <v>7</v>
       </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>31</v>
+      <c r="O10">
+        <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="S10" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="T10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="U10" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" t="s">
+        <v>35</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1627,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1639,40 +824,43 @@
         <v>43</v>
       </c>
       <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
       <c r="I11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="M11" t="s">
+        <v>50</v>
       </c>
       <c r="R11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S11" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="T11" t="s">
-        <v>30</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="U11" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" t="s">
+        <v>35</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1680,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1692,37 +880,40 @@
         <v>41</v>
       </c>
       <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
         <v>30</v>
       </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J12">
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>52</v>
       </c>
       <c r="R12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" t="s">
         <v>45</v>
       </c>
-      <c r="S12" t="s">
-        <v>31</v>
-      </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="T12" t="s">
+        <v>53</v>
+      </c>
+      <c r="U12" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1730,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1742,40 +933,43 @@
         <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>38</v>
-      </c>
-      <c r="M13">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="N13">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
       </c>
       <c r="R13" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S13" t="s">
-        <v>31</v>
-      </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="T13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U13" t="s">
+        <v>36</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1783,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -1795,40 +989,43 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J14">
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14">
+        <v>32</v>
+      </c>
+      <c r="N14">
         <v>24</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>8</v>
       </c>
-      <c r="Q14" t="s">
-        <v>30</v>
-      </c>
       <c r="R14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>31</v>
-      </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="T14" t="s">
+        <v>49</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1836,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1848,37 +1045,40 @@
         <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" t="s">
         <v>44</v>
       </c>
-      <c r="Q15" t="s">
-        <v>30</v>
+      <c r="M15" t="s">
+        <v>52</v>
       </c>
       <c r="R15" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="T15" t="s">
+        <v>56</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1886,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1898,37 +1098,40 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J16">
         <v>9</v>
       </c>
       <c r="K16" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>58</v>
       </c>
       <c r="R16" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="S16" t="s">
-        <v>31</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="T16" t="s">
+        <v>60</v>
+      </c>
+      <c r="U16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1936,7 +1139,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1945,19 +1148,19 @@
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
-      </c>
-      <c r="U17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1965,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1974,19 +1177,19 @@
         <v>-40</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
-      </c>
-      <c r="U18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="X18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1994,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2006,31 +1209,34 @@
         <v>-20</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J19">
         <v>11</v>
       </c>
       <c r="K19" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="R19" t="s">
+        <v>36</v>
       </c>
       <c r="S19" t="s">
-        <v>30</v>
-      </c>
-      <c r="U19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="U19" t="s">
+        <v>35</v>
+      </c>
+      <c r="X19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2038,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2050,31 +1256,34 @@
         <v>-31</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="R20" t="s">
+        <v>35</v>
       </c>
       <c r="S20" t="s">
-        <v>30</v>
-      </c>
-      <c r="U20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="U20" t="s">
+        <v>35</v>
+      </c>
+      <c r="X20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2082,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2094,31 +1303,34 @@
         <v>-31</v>
       </c>
       <c r="G21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
         <v>31</v>
       </c>
-      <c r="H21" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" t="s">
-        <v>27</v>
-      </c>
       <c r="J21">
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>35</v>
       </c>
       <c r="S21" t="s">
-        <v>31</v>
-      </c>
-      <c r="U21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="U21" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2126,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -2138,34 +1350,37 @@
         <v>-33</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>36</v>
       </c>
       <c r="S22" t="s">
-        <v>31</v>
-      </c>
-      <c r="T22" t="s">
-        <v>30</v>
-      </c>
-      <c r="U22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="U22" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" t="s">
+        <v>35</v>
+      </c>
+      <c r="X22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2173,7 +1388,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -2185,22 +1400,22 @@
         <v>-34</v>
       </c>
       <c r="G23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" t="s">
+        <v>40</v>
+      </c>
+      <c r="I23" t="s">
+        <v>63</v>
+      </c>
+      <c r="P23">
         <v>31</v>
       </c>
-      <c r="H23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" t="s">
-        <v>53</v>
-      </c>
-      <c r="O23">
-        <v>31</v>
-      </c>
-      <c r="U23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="X23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2208,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2220,43 +1435,46 @@
         <v>-36</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>38</v>
-      </c>
-      <c r="M24">
+        <v>44</v>
+      </c>
+      <c r="N24">
         <v>14</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>5</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>0</v>
       </c>
-      <c r="Q24" t="s">
-        <v>30</v>
-      </c>
       <c r="R24" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>31</v>
-      </c>
-      <c r="U24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="T24" t="s">
+        <v>64</v>
+      </c>
+      <c r="U24" t="s">
+        <v>36</v>
+      </c>
+      <c r="X24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2264,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2276,37 +1494,40 @@
         <v>-36</v>
       </c>
       <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" t="s">
         <v>30</v>
       </c>
-      <c r="H25" t="s">
-        <v>26</v>
-      </c>
       <c r="I25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J25">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>28</v>
-      </c>
-      <c r="L25" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>50</v>
       </c>
       <c r="R25" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="S25" t="s">
-        <v>31</v>
-      </c>
-      <c r="U25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+      <c r="T25" t="s">
+        <v>60</v>
+      </c>
+      <c r="U25" t="s">
+        <v>36</v>
+      </c>
+      <c r="X25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2314,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2326,34 +1547,34 @@
         <v>-49</v>
       </c>
       <c r="G26" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I26" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
-      </c>
-      <c r="N26">
-        <v>3</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>31</v>
-      </c>
-      <c r="S26" t="s">
-        <v>31</v>
-      </c>
-      <c r="U26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="R26" t="s">
+        <v>36</v>
+      </c>
+      <c r="U26" t="s">
+        <v>36</v>
+      </c>
+      <c r="X26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2361,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2373,43 +1594,46 @@
         <v>-49</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M27">
+        <v>32</v>
+      </c>
+      <c r="N27">
         <v>0</v>
       </c>
-      <c r="N27">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>30</v>
+      <c r="O27">
+        <v>2</v>
       </c>
       <c r="R27" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T27" t="s">
-        <v>30</v>
-      </c>
-      <c r="U27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="U27" t="s">
+        <v>35</v>
+      </c>
+      <c r="V27" t="s">
+        <v>35</v>
+      </c>
+      <c r="X27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2417,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -2429,43 +1653,46 @@
         <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J28">
         <v>9</v>
       </c>
       <c r="K28" t="s">
-        <v>28</v>
-      </c>
-      <c r="M28">
+        <v>32</v>
+      </c>
+      <c r="N28">
         <v>4</v>
       </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>31</v>
+      <c r="O28">
+        <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="S28" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="T28" t="s">
-        <v>30</v>
-      </c>
-      <c r="U28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="U28" t="s">
+        <v>35</v>
+      </c>
+      <c r="V28" t="s">
+        <v>35</v>
+      </c>
+      <c r="X28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2473,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2485,40 +1712,43 @@
         <v>34</v>
       </c>
       <c r="G29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" t="s">
         <v>30</v>
       </c>
-      <c r="H29" t="s">
-        <v>26</v>
-      </c>
       <c r="I29" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29" t="s">
-        <v>28</v>
-      </c>
-      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" t="s">
+        <v>67</v>
+      </c>
+      <c r="R29" t="s">
+        <v>36</v>
+      </c>
+      <c r="S29" t="s">
+        <v>45</v>
+      </c>
+      <c r="T29" t="s">
         <v>56</v>
       </c>
-      <c r="Q29" t="s">
-        <v>31</v>
-      </c>
-      <c r="R29" t="s">
-        <v>47</v>
-      </c>
-      <c r="S29" t="s">
-        <v>31</v>
-      </c>
-      <c r="T29" t="s">
-        <v>30</v>
-      </c>
-      <c r="U29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U29" t="s">
+        <v>36</v>
+      </c>
+      <c r="V29" t="s">
+        <v>35</v>
+      </c>
+      <c r="X29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2526,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -2538,40 +1768,43 @@
         <v>29</v>
       </c>
       <c r="G30" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J30">
         <v>6</v>
       </c>
       <c r="K30" t="s">
-        <v>28</v>
-      </c>
-      <c r="M30">
+        <v>32</v>
+      </c>
+      <c r="N30">
         <v>7</v>
       </c>
-      <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>31</v>
+      <c r="O30">
+        <v>1</v>
       </c>
       <c r="R30" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S30" t="s">
-        <v>30</v>
-      </c>
-      <c r="U30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="T30" t="s">
+        <v>54</v>
+      </c>
+      <c r="U30" t="s">
+        <v>35</v>
+      </c>
+      <c r="X30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2579,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2591,40 +1824,43 @@
         <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I31" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>38</v>
-      </c>
-      <c r="M31">
+        <v>44</v>
+      </c>
+      <c r="N31">
         <v>11</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>5</v>
       </c>
-      <c r="Q31" t="s">
-        <v>30</v>
-      </c>
       <c r="R31" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>31</v>
-      </c>
-      <c r="U31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="T31" t="s">
+        <v>68</v>
+      </c>
+      <c r="U31" t="s">
+        <v>36</v>
+      </c>
+      <c r="X31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2632,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2644,40 +1880,43 @@
         <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J32">
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>28</v>
-      </c>
-      <c r="M32">
+        <v>32</v>
+      </c>
+      <c r="N32">
         <v>0</v>
       </c>
-      <c r="N32">
-        <v>3</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>31</v>
+      <c r="O32">
+        <v>3</v>
       </c>
       <c r="R32" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S32" t="s">
-        <v>31</v>
-      </c>
-      <c r="U32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="T32" t="s">
+        <v>48</v>
+      </c>
+      <c r="U32" t="s">
+        <v>36</v>
+      </c>
+      <c r="X32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2685,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2697,40 +1936,43 @@
         <v>8</v>
       </c>
       <c r="G33" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" t="s">
         <v>31</v>
-      </c>
-      <c r="H33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I33" t="s">
-        <v>27</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L33" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>52</v>
       </c>
       <c r="R33" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="T33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+      <c r="U33" t="s">
+        <v>35</v>
+      </c>
+      <c r="V33" t="s">
+        <v>35</v>
+      </c>
+      <c r="X33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2738,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2750,37 +1992,40 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" t="s">
         <v>31</v>
-      </c>
-      <c r="H34" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" t="s">
-        <v>27</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" t="s">
+        <v>44</v>
+      </c>
+      <c r="M34" t="s">
+        <v>67</v>
+      </c>
+      <c r="R34" t="s">
+        <v>36</v>
+      </c>
+      <c r="S34" t="s">
+        <v>59</v>
+      </c>
+      <c r="T34" t="s">
         <v>56</v>
       </c>
-      <c r="Q34" t="s">
-        <v>31</v>
-      </c>
-      <c r="R34" t="s">
-        <v>47</v>
-      </c>
-      <c r="S34" t="s">
-        <v>31</v>
-      </c>
-      <c r="U34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U34" t="s">
+        <v>36</v>
+      </c>
+      <c r="X34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2788,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -2800,25 +2045,25 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>30</v>
-      </c>
-      <c r="U35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="R35" t="s">
+        <v>35</v>
+      </c>
+      <c r="X35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2826,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2838,90 +2083,96 @@
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q36" t="s">
+        <v>44</v>
+      </c>
+      <c r="M36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R36" t="s">
+        <v>35</v>
+      </c>
+      <c r="S36" t="s">
+        <v>47</v>
+      </c>
+      <c r="T36" t="s">
+        <v>70</v>
+      </c>
+      <c r="U36" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" t="s">
         <v>30</v>
       </c>
-      <c r="R36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S36" t="s">
-        <v>30</v>
-      </c>
-      <c r="U36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" t="s">
-        <v>26</v>
-      </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>28</v>
-      </c>
-      <c r="L37" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" t="s">
+        <v>67</v>
+      </c>
+      <c r="R37" t="s">
+        <v>36</v>
+      </c>
+      <c r="S37" t="s">
+        <v>47</v>
+      </c>
+      <c r="T37" t="s">
         <v>56</v>
       </c>
-      <c r="Q37" t="s">
-        <v>31</v>
-      </c>
-      <c r="R37" t="s">
-        <v>47</v>
-      </c>
-      <c r="S37" t="s">
-        <v>31</v>
-      </c>
-      <c r="T37" t="s">
-        <v>30</v>
-      </c>
-      <c r="U37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U37" t="s">
+        <v>36</v>
+      </c>
+      <c r="V37" t="s">
+        <v>35</v>
+      </c>
+      <c r="X37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2929,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2938,19 +2189,19 @@
         <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
-      </c>
-      <c r="U38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="X38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2958,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2967,19 +2218,19 @@
         <v>-40</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H39" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I39" t="s">
-        <v>24</v>
-      </c>
-      <c r="U39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="X39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2987,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2999,31 +2250,34 @@
         <v>-20</v>
       </c>
       <c r="G40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" t="s">
         <v>31</v>
-      </c>
-      <c r="H40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I40" t="s">
-        <v>27</v>
       </c>
       <c r="J40">
         <v>-4</v>
       </c>
       <c r="K40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="R40" t="s">
+        <v>35</v>
       </c>
       <c r="S40" t="s">
-        <v>31</v>
-      </c>
-      <c r="U40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="U40" t="s">
+        <v>36</v>
+      </c>
+      <c r="X40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3031,7 +2285,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -3043,31 +2297,34 @@
         <v>-16</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I41" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" t="s">
+        <v>36</v>
       </c>
       <c r="S41" t="s">
-        <v>30</v>
-      </c>
-      <c r="U41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="U41" t="s">
+        <v>35</v>
+      </c>
+      <c r="X41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3075,7 +2332,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>3</v>
@@ -3087,31 +2344,34 @@
         <v>-16</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I42" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J42">
         <v>-4</v>
       </c>
       <c r="K42" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R42" t="s">
+        <v>33</v>
       </c>
       <c r="S42" t="s">
-        <v>30</v>
-      </c>
-      <c r="U42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="U42" t="s">
+        <v>35</v>
+      </c>
+      <c r="X42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3119,7 +2379,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -3131,19 +2391,19 @@
         <v>-12</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I43" t="s">
-        <v>61</v>
-      </c>
-      <c r="U43">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="X43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3151,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3163,40 +2423,43 @@
         <v>38</v>
       </c>
       <c r="G44" t="s">
+        <v>36</v>
+      </c>
+      <c r="H44" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" t="s">
         <v>31</v>
-      </c>
-      <c r="H44" t="s">
-        <v>26</v>
-      </c>
-      <c r="I44" t="s">
-        <v>27</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" t="s">
-        <v>42</v>
-      </c>
-      <c r="P44">
+        <v>44</v>
+      </c>
+      <c r="M44" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q44">
         <v>0</v>
       </c>
-      <c r="Q44" t="s">
-        <v>31</v>
-      </c>
       <c r="R44" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="S44" t="s">
-        <v>31</v>
-      </c>
-      <c r="U44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="T44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U44" t="s">
+        <v>36</v>
+      </c>
+      <c r="X44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3204,7 +2467,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -3216,25 +2479,25 @@
         <v>38</v>
       </c>
       <c r="G45" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I45" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>31</v>
-      </c>
-      <c r="U45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="R45" t="s">
+        <v>36</v>
+      </c>
+      <c r="X45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3242,13 +2505,13 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="R46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3256,7 +2519,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -3268,34 +2531,37 @@
         <v>38</v>
       </c>
       <c r="G47" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I47" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J47">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R47" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>30</v>
-      </c>
-      <c r="U47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="T47" t="s">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s">
+        <v>35</v>
+      </c>
+      <c r="X47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3303,7 +2569,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3315,37 +2581,40 @@
         <v>25</v>
       </c>
       <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" t="s">
         <v>30</v>
       </c>
-      <c r="H48" t="s">
-        <v>26</v>
-      </c>
       <c r="I48" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J48">
         <v>-3</v>
       </c>
       <c r="K48" t="s">
-        <v>38</v>
-      </c>
-      <c r="L48" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="M48" t="s">
+        <v>67</v>
       </c>
       <c r="R48" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S48" t="s">
-        <v>31</v>
-      </c>
-      <c r="U48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="T48" t="s">
+        <v>54</v>
+      </c>
+      <c r="U48" t="s">
+        <v>36</v>
+      </c>
+      <c r="X48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3353,7 +2622,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -3365,40 +2634,43 @@
         <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I49" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>38</v>
-      </c>
-      <c r="M49">
+        <v>44</v>
+      </c>
+      <c r="N49">
         <v>32</v>
       </c>
-      <c r="N49">
+      <c r="O49">
         <v>7</v>
       </c>
-      <c r="Q49" t="s">
-        <v>31</v>
-      </c>
       <c r="R49" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="S49" t="s">
-        <v>30</v>
-      </c>
-      <c r="U49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="T49" t="s">
+        <v>49</v>
+      </c>
+      <c r="U49" t="s">
+        <v>35</v>
+      </c>
+      <c r="X49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3406,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3418,28 +2690,31 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J50">
         <v>-5</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>31</v>
-      </c>
-      <c r="T50" t="s">
-        <v>30</v>
-      </c>
-      <c r="U50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="R50" t="s">
+        <v>36</v>
+      </c>
+      <c r="S50" t="s">
+        <v>45</v>
+      </c>
+      <c r="V50" t="s">
+        <v>35</v>
+      </c>
+      <c r="X50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3447,7 +2722,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3459,40 +2734,43 @@
         <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J51">
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>28</v>
-      </c>
-      <c r="M51">
+        <v>32</v>
+      </c>
+      <c r="N51">
         <v>6</v>
       </c>
-      <c r="N51">
-        <v>2</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>31</v>
+      <c r="O51">
+        <v>2</v>
       </c>
       <c r="R51" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="S51" t="s">
-        <v>30</v>
-      </c>
-      <c r="U51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="T51" t="s">
+        <v>64</v>
+      </c>
+      <c r="U51" t="s">
+        <v>35</v>
+      </c>
+      <c r="X51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3500,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -3512,37 +2790,40 @@
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I52" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J52">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>28</v>
-      </c>
-      <c r="L52" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="M52" t="s">
+        <v>52</v>
       </c>
       <c r="R52" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="S52" t="s">
-        <v>31</v>
-      </c>
-      <c r="U52">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="T52" t="s">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s">
+        <v>36</v>
+      </c>
+      <c r="X52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3550,7 +2831,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -3562,37 +2843,40 @@
         <v>5</v>
       </c>
       <c r="G53" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J53">
         <v>3</v>
       </c>
       <c r="K53" t="s">
-        <v>28</v>
-      </c>
-      <c r="L53" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="M53" t="s">
+        <v>52</v>
       </c>
       <c r="R53" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="S53" t="s">
-        <v>30</v>
-      </c>
-      <c r="U53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="T53" t="s">
+        <v>79</v>
+      </c>
+      <c r="U53" t="s">
+        <v>35</v>
+      </c>
+      <c r="X53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3600,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3612,40 +2896,43 @@
         <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H54" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I54" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J54">
         <v>-1</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="M54" t="s">
+        <v>67</v>
       </c>
       <c r="R54" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="S54" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="T54" t="s">
-        <v>30</v>
-      </c>
-      <c r="U54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="U54" t="s">
+        <v>36</v>
+      </c>
+      <c r="V54" t="s">
+        <v>35</v>
+      </c>
+      <c r="X54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3653,7 +2940,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3665,37 +2952,40 @@
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H55" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I55" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J55">
         <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>28</v>
-      </c>
-      <c r="L55" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="M55" t="s">
+        <v>58</v>
       </c>
       <c r="R55" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="S55" t="s">
-        <v>30</v>
-      </c>
-      <c r="U55">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="T55" t="s">
+        <v>80</v>
+      </c>
+      <c r="U55" t="s">
+        <v>35</v>
+      </c>
+      <c r="X55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3703,7 +2993,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -3715,19 +3005,19 @@
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H56" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I56" t="s">
-        <v>52</v>
-      </c>
-      <c r="U56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="X56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3735,22 +3025,22 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F57">
         <v>-40</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H57" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I57" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3758,7 +3048,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3770,31 +3060,34 @@
         <v>-20</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H58" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I58" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J58">
         <v>-6</v>
       </c>
       <c r="K58" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R58" t="s">
+        <v>33</v>
       </c>
       <c r="S58" t="s">
-        <v>30</v>
-      </c>
-      <c r="U58">
+        <v>34</v>
+      </c>
+      <c r="U58" t="s">
+        <v>35</v>
+      </c>
+      <c r="X58">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3802,7 +3095,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3814,40 +3107,43 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
+        <v>36</v>
+      </c>
+      <c r="H59" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" t="s">
         <v>31</v>
-      </c>
-      <c r="H59" t="s">
-        <v>26</v>
-      </c>
-      <c r="I59" t="s">
-        <v>27</v>
       </c>
       <c r="J59">
         <v>-10</v>
       </c>
       <c r="K59" t="s">
-        <v>38</v>
-      </c>
-      <c r="L59" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="M59" t="s">
+        <v>50</v>
       </c>
       <c r="R59" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="S59" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="T59" t="s">
-        <v>30</v>
-      </c>
-      <c r="U59">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s">
+        <v>35</v>
+      </c>
+      <c r="V59" t="s">
+        <v>35</v>
+      </c>
+      <c r="X59">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3855,7 +3151,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3867,40 +3163,43 @@
         <v>24</v>
       </c>
       <c r="G60" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H60" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I60" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>38</v>
-      </c>
-      <c r="M60">
+        <v>44</v>
+      </c>
+      <c r="N60">
         <v>24</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>4</v>
       </c>
-      <c r="Q60" t="s">
-        <v>30</v>
-      </c>
       <c r="R60" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="S60" t="s">
-        <v>30</v>
-      </c>
-      <c r="U60">
+        <v>71</v>
+      </c>
+      <c r="T60" t="s">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s">
+        <v>35</v>
+      </c>
+      <c r="X60">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3908,7 +3207,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -3920,40 +3219,43 @@
         <v>5</v>
       </c>
       <c r="G61" t="s">
+        <v>35</v>
+      </c>
+      <c r="H61" t="s">
         <v>30</v>
       </c>
-      <c r="H61" t="s">
-        <v>26</v>
-      </c>
       <c r="I61" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>28</v>
-      </c>
-      <c r="L61" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="M61" t="s">
+        <v>50</v>
       </c>
       <c r="R61" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S61" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="T61" t="s">
-        <v>31</v>
-      </c>
-      <c r="U61">
+        <v>51</v>
+      </c>
+      <c r="U61" t="s">
+        <v>36</v>
+      </c>
+      <c r="V61" t="s">
+        <v>36</v>
+      </c>
+      <c r="X61">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3961,7 +3263,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3973,37 +3275,40 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I62" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>28</v>
-      </c>
-      <c r="L62" t="s">
+        <v>32</v>
+      </c>
+      <c r="M62" t="s">
+        <v>67</v>
+      </c>
+      <c r="R62" t="s">
+        <v>36</v>
+      </c>
+      <c r="S62" t="s">
+        <v>59</v>
+      </c>
+      <c r="T62" t="s">
         <v>56</v>
       </c>
-      <c r="Q62" t="s">
-        <v>31</v>
-      </c>
-      <c r="R62" t="s">
-        <v>47</v>
-      </c>
-      <c r="S62" t="s">
-        <v>31</v>
-      </c>
-      <c r="U62">
+      <c r="U62" t="s">
+        <v>36</v>
+      </c>
+      <c r="X62">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4011,7 +3316,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -4023,22 +3328,22 @@
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H63" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I63" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
-      <c r="U63">
+      <c r="X63">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4046,7 +3351,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -4055,25 +3360,25 @@
         <v>-40</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I64" t="s">
-        <v>71</v>
-      </c>
-      <c r="O64">
+        <v>84</v>
+      </c>
+      <c r="P64">
         <v>56</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>63</v>
       </c>
-      <c r="U64">
+      <c r="X64">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4081,7 +3386,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -4093,34 +3398,37 @@
         <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I65" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R65" t="s">
+        <v>36</v>
       </c>
       <c r="S65" t="s">
-        <v>30</v>
-      </c>
-      <c r="T65" t="s">
-        <v>31</v>
-      </c>
-      <c r="U65">
+        <v>85</v>
+      </c>
+      <c r="U65" t="s">
+        <v>35</v>
+      </c>
+      <c r="V65" t="s">
+        <v>36</v>
+      </c>
+      <c r="X65">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4128,7 +3436,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -4140,31 +3448,34 @@
         <v>30</v>
       </c>
       <c r="G66" t="s">
+        <v>36</v>
+      </c>
+      <c r="H66" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" t="s">
         <v>31</v>
-      </c>
-      <c r="H66" t="s">
-        <v>26</v>
-      </c>
-      <c r="I66" t="s">
-        <v>27</v>
       </c>
       <c r="J66">
         <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="R66" t="s">
+        <v>35</v>
       </c>
       <c r="S66" t="s">
-        <v>31</v>
-      </c>
-      <c r="U66">
+        <v>45</v>
+      </c>
+      <c r="U66" t="s">
+        <v>36</v>
+      </c>
+      <c r="X66">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4172,7 +3483,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -4184,34 +3495,37 @@
         <v>24</v>
       </c>
       <c r="G67" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I67" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="R67" t="s">
+        <v>35</v>
       </c>
       <c r="S67" t="s">
-        <v>30</v>
-      </c>
-      <c r="T67" t="s">
-        <v>30</v>
-      </c>
-      <c r="U67">
+        <v>45</v>
+      </c>
+      <c r="U67" t="s">
+        <v>35</v>
+      </c>
+      <c r="V67" t="s">
+        <v>35</v>
+      </c>
+      <c r="X67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4219,7 +3533,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -4231,22 +3545,22 @@
         <v>24</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>28</v>
-      </c>
-      <c r="U68">
+        <v>32</v>
+      </c>
+      <c r="X68">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4254,7 +3568,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D69">
         <v>4</v>
@@ -4266,31 +3580,34 @@
         <v>24</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H69" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I69" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R69" t="s">
+        <v>36</v>
       </c>
       <c r="S69" t="s">
-        <v>31</v>
-      </c>
-      <c r="U69">
+        <v>85</v>
+      </c>
+      <c r="U69" t="s">
+        <v>36</v>
+      </c>
+      <c r="X69">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4298,7 +3615,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -4310,40 +3627,43 @@
         <v>-23</v>
       </c>
       <c r="G70" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H70" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I70" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>38</v>
-      </c>
-      <c r="M70">
+        <v>44</v>
+      </c>
+      <c r="N70">
         <v>0</v>
       </c>
-      <c r="N70">
-        <v>3</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>30</v>
+      <c r="O70">
+        <v>3</v>
       </c>
       <c r="R70" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="S70" t="s">
-        <v>31</v>
-      </c>
-      <c r="U70">
+        <v>71</v>
+      </c>
+      <c r="T70" t="s">
+        <v>64</v>
+      </c>
+      <c r="U70" t="s">
+        <v>36</v>
+      </c>
+      <c r="X70">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4351,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4363,40 +3683,43 @@
         <v>-23</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H71" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I71" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J71">
         <v>19</v>
       </c>
       <c r="K71" t="s">
-        <v>28</v>
-      </c>
-      <c r="M71">
+        <v>32</v>
+      </c>
+      <c r="N71">
         <v>16</v>
       </c>
-      <c r="N71">
-        <v>3</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>30</v>
+      <c r="O71">
+        <v>3</v>
       </c>
       <c r="R71" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S71" t="s">
-        <v>31</v>
-      </c>
-      <c r="U71">
+        <v>45</v>
+      </c>
+      <c r="T71" t="s">
+        <v>46</v>
+      </c>
+      <c r="U71" t="s">
+        <v>36</v>
+      </c>
+      <c r="X71">
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4404,7 +3727,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -4416,34 +3739,37 @@
         <v>-42</v>
       </c>
       <c r="G72" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H72" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I72" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J72">
         <v>-8</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="R72" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="S72" t="s">
-        <v>31</v>
-      </c>
-      <c r="U72">
+        <v>45</v>
+      </c>
+      <c r="T72" t="s">
+        <v>64</v>
+      </c>
+      <c r="U72" t="s">
+        <v>36</v>
+      </c>
+      <c r="X72">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4451,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -4463,25 +3789,28 @@
         <v>-34</v>
       </c>
       <c r="G73" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I73" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J73">
         <v>5</v>
       </c>
       <c r="K73" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>30</v>
-      </c>
-      <c r="U73">
+        <v>44</v>
+      </c>
+      <c r="R73" t="s">
+        <v>35</v>
+      </c>
+      <c r="S73" t="s">
+        <v>45</v>
+      </c>
+      <c r="X73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4489,7 +3818,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -4501,43 +3830,46 @@
         <v>-39</v>
       </c>
       <c r="G74" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J74">
         <v>28</v>
       </c>
       <c r="K74" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74">
+        <v>32</v>
+      </c>
+      <c r="N74">
         <v>25</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>8</v>
       </c>
-      <c r="Q74" t="s">
-        <v>30</v>
-      </c>
       <c r="R74" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S74" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="T74" t="s">
-        <v>31</v>
-      </c>
-      <c r="U74">
+        <v>49</v>
+      </c>
+      <c r="U74" t="s">
+        <v>35</v>
+      </c>
+      <c r="V74" t="s">
+        <v>36</v>
+      </c>
+      <c r="X74">
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4545,7 +3877,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -4557,37 +3889,40 @@
         <v>33</v>
       </c>
       <c r="G75" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H75" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I75" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J75">
         <v>4</v>
       </c>
       <c r="K75" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75">
+        <v>32</v>
+      </c>
+      <c r="N75">
         <v>0</v>
       </c>
-      <c r="Q75" t="s">
-        <v>30</v>
-      </c>
       <c r="R75" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="S75" t="s">
-        <v>30</v>
-      </c>
-      <c r="U75">
+        <v>45</v>
+      </c>
+      <c r="T75" t="s">
+        <v>66</v>
+      </c>
+      <c r="U75" t="s">
+        <v>35</v>
+      </c>
+      <c r="X75">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4595,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4607,40 +3942,43 @@
         <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H76" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I76" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J76">
         <v>29</v>
       </c>
       <c r="K76" t="s">
-        <v>28</v>
-      </c>
-      <c r="M76">
+        <v>32</v>
+      </c>
+      <c r="N76">
         <v>19</v>
       </c>
-      <c r="N76">
+      <c r="O76">
         <v>8</v>
       </c>
-      <c r="Q76" t="s">
-        <v>31</v>
-      </c>
       <c r="R76" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="S76" t="s">
-        <v>30</v>
-      </c>
-      <c r="U76">
+        <v>45</v>
+      </c>
+      <c r="T76" t="s">
+        <v>49</v>
+      </c>
+      <c r="U76" t="s">
+        <v>35</v>
+      </c>
+      <c r="X76">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4648,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4660,19 +3998,19 @@
         <v>3</v>
       </c>
       <c r="G77" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H77" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I77" t="s">
-        <v>52</v>
-      </c>
-      <c r="U77">
+        <v>62</v>
+      </c>
+      <c r="X77">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4680,7 +4018,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4689,19 +4027,19 @@
         <v>-40</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I78" t="s">
-        <v>71</v>
-      </c>
-      <c r="U78">
+        <v>84</v>
+      </c>
+      <c r="X78">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4709,7 +4047,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -4721,31 +4059,34 @@
         <v>-20</v>
       </c>
       <c r="G79" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" t="s">
         <v>31</v>
-      </c>
-      <c r="H79" t="s">
-        <v>26</v>
-      </c>
-      <c r="I79" t="s">
-        <v>27</v>
       </c>
       <c r="J79">
         <v>20</v>
       </c>
       <c r="K79" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="R79" t="s">
+        <v>36</v>
       </c>
       <c r="S79" t="s">
-        <v>30</v>
-      </c>
-      <c r="U79">
+        <v>71</v>
+      </c>
+      <c r="U79" t="s">
+        <v>35</v>
+      </c>
+      <c r="X79">
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4753,31 +4094,31 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F80">
         <v>-40</v>
       </c>
       <c r="G80" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H80" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="I80" t="s">
-        <v>71</v>
-      </c>
-      <c r="O80">
+        <v>84</v>
+      </c>
+      <c r="P80">
         <v>57</v>
       </c>
-      <c r="P80">
+      <c r="Q80">
         <v>40</v>
       </c>
-      <c r="U80">
+      <c r="X80">
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4785,7 +4126,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4797,37 +4138,40 @@
         <v>-43</v>
       </c>
       <c r="G81" t="s">
+        <v>36</v>
+      </c>
+      <c r="H81" t="s">
+        <v>30</v>
+      </c>
+      <c r="I81" t="s">
         <v>31</v>
       </c>
-      <c r="H81" t="s">
-        <v>26</v>
-      </c>
-      <c r="I81" t="s">
-        <v>27</v>
-      </c>
       <c r="J81">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>38</v>
-      </c>
-      <c r="L81" t="s">
+        <v>44</v>
+      </c>
+      <c r="M81" t="s">
+        <v>67</v>
+      </c>
+      <c r="R81" t="s">
+        <v>36</v>
+      </c>
+      <c r="S81" t="s">
+        <v>71</v>
+      </c>
+      <c r="T81" t="s">
         <v>56</v>
       </c>
-      <c r="Q81" t="s">
-        <v>31</v>
-      </c>
-      <c r="R81" t="s">
-        <v>47</v>
-      </c>
-      <c r="S81" t="s">
-        <v>31</v>
-      </c>
-      <c r="U81">
+      <c r="U81" t="s">
+        <v>36</v>
+      </c>
+      <c r="X81">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4835,7 +4179,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -4847,43 +4191,46 @@
         <v>-44</v>
       </c>
       <c r="G82" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H82" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I82" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J82">
         <v>-3</v>
       </c>
       <c r="K82" t="s">
-        <v>38</v>
-      </c>
-      <c r="M82">
+        <v>44</v>
+      </c>
+      <c r="N82">
         <v>0</v>
       </c>
-      <c r="N82">
-        <v>3</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>31</v>
+      <c r="O82">
+        <v>3</v>
       </c>
       <c r="R82" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="S82" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="T82" t="s">
-        <v>30</v>
-      </c>
-      <c r="U82">
+        <v>66</v>
+      </c>
+      <c r="U82" t="s">
+        <v>36</v>
+      </c>
+      <c r="V82" t="s">
+        <v>35</v>
+      </c>
+      <c r="X82">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4891,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -4903,34 +4250,37 @@
         <v>-41</v>
       </c>
       <c r="G83" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H83" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I83" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J83">
         <v>5</v>
       </c>
       <c r="K83" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="R83" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S83" t="s">
-        <v>31</v>
-      </c>
-      <c r="U83">
+        <v>45</v>
+      </c>
+      <c r="T83" t="s">
+        <v>49</v>
+      </c>
+      <c r="U83" t="s">
+        <v>36</v>
+      </c>
+      <c r="X83">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4938,7 +4288,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -4950,40 +4300,43 @@
         <v>-36</v>
       </c>
       <c r="G84" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H84" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I84" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J84">
         <v>23</v>
       </c>
       <c r="K84" t="s">
-        <v>28</v>
-      </c>
-      <c r="M84">
+        <v>32</v>
+      </c>
+      <c r="N84">
         <v>14</v>
       </c>
-      <c r="N84">
+      <c r="O84">
         <v>5</v>
       </c>
-      <c r="Q84" t="s">
-        <v>30</v>
-      </c>
       <c r="R84" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S84" t="s">
-        <v>30</v>
-      </c>
-      <c r="U84">
+        <v>45</v>
+      </c>
+      <c r="T84" t="s">
+        <v>49</v>
+      </c>
+      <c r="U84" t="s">
+        <v>35</v>
+      </c>
+      <c r="X84">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4991,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -5003,37 +4356,40 @@
         <v>41</v>
       </c>
       <c r="G85" t="s">
+        <v>36</v>
+      </c>
+      <c r="H85" t="s">
+        <v>30</v>
+      </c>
+      <c r="I85" t="s">
         <v>31</v>
       </c>
-      <c r="H85" t="s">
-        <v>26</v>
-      </c>
-      <c r="I85" t="s">
-        <v>27</v>
-      </c>
       <c r="J85">
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>38</v>
-      </c>
-      <c r="L85" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="M85" t="s">
+        <v>50</v>
       </c>
       <c r="R85" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="S85" t="s">
-        <v>31</v>
-      </c>
-      <c r="U85">
+        <v>83</v>
+      </c>
+      <c r="T85" t="s">
+        <v>60</v>
+      </c>
+      <c r="U85" t="s">
+        <v>36</v>
+      </c>
+      <c r="X85">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5041,7 +4397,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -5053,40 +4409,43 @@
         <v>39</v>
       </c>
       <c r="G86" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H86" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I86" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>38</v>
-      </c>
-      <c r="M86">
+        <v>44</v>
+      </c>
+      <c r="N86">
         <v>26</v>
       </c>
-      <c r="N86">
+      <c r="O86">
         <v>9</v>
       </c>
-      <c r="Q86" t="s">
-        <v>30</v>
-      </c>
       <c r="R86" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="S86" t="s">
-        <v>31</v>
-      </c>
-      <c r="U86">
+        <v>55</v>
+      </c>
+      <c r="T86" t="s">
+        <v>88</v>
+      </c>
+      <c r="U86" t="s">
+        <v>36</v>
+      </c>
+      <c r="X86">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5094,7 +4453,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -5106,40 +4465,43 @@
         <v>39</v>
       </c>
       <c r="G87" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H87" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I87" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J87">
         <v>39</v>
       </c>
       <c r="K87" t="s">
-        <v>28</v>
-      </c>
-      <c r="M87">
+        <v>32</v>
+      </c>
+      <c r="N87">
         <v>34</v>
       </c>
-      <c r="N87">
+      <c r="O87">
         <v>9</v>
       </c>
-      <c r="Q87" t="s">
-        <v>30</v>
-      </c>
       <c r="R87" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="S87" t="s">
-        <v>31</v>
-      </c>
-      <c r="U87">
+        <v>45</v>
+      </c>
+      <c r="T87" t="s">
+        <v>64</v>
+      </c>
+      <c r="U87" t="s">
+        <v>36</v>
+      </c>
+      <c r="X87">
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5147,7 +4509,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -5156,19 +4518,22 @@
         <v>3</v>
       </c>
       <c r="G88" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H88" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I88" t="s">
-        <v>52</v>
-      </c>
-      <c r="U88">
+        <v>62</v>
+      </c>
+      <c r="J88">
+        <v>3</v>
+      </c>
+      <c r="X88">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5176,34 +4541,37 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
+      <c r="E89">
+        <v>10</v>
+      </c>
       <c r="F89">
         <v>-40</v>
       </c>
       <c r="G89" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I89" t="s">
-        <v>71</v>
-      </c>
-      <c r="O89">
+        <v>84</v>
+      </c>
+      <c r="P89">
         <v>59</v>
       </c>
-      <c r="P89">
+      <c r="Q89">
         <v>20</v>
       </c>
-      <c r="U89">
+      <c r="X89">
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5211,7 +4579,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -5223,31 +4591,34 @@
         <v>-10</v>
       </c>
       <c r="G90" t="s">
+        <v>35</v>
+      </c>
+      <c r="H90" t="s">
         <v>30</v>
       </c>
-      <c r="H90" t="s">
-        <v>26</v>
-      </c>
       <c r="I90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R90" t="s">
+        <v>36</v>
       </c>
       <c r="S90" t="s">
-        <v>31</v>
-      </c>
-      <c r="U90">
+        <v>71</v>
+      </c>
+      <c r="U90" t="s">
+        <v>36</v>
+      </c>
+      <c r="X90">
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5255,7 +4626,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -5267,31 +4638,34 @@
         <v>-13</v>
       </c>
       <c r="G91" t="s">
+        <v>36</v>
+      </c>
+      <c r="H91" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" t="s">
         <v>31</v>
-      </c>
-      <c r="H91" t="s">
-        <v>26</v>
-      </c>
-      <c r="I91" t="s">
-        <v>27</v>
       </c>
       <c r="J91">
         <v>24</v>
       </c>
       <c r="K91" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>29</v>
+        <v>44</v>
+      </c>
+      <c r="R91" t="s">
+        <v>33</v>
       </c>
       <c r="S91" t="s">
-        <v>31</v>
-      </c>
-      <c r="U91">
+        <v>34</v>
+      </c>
+      <c r="U91" t="s">
+        <v>36</v>
+      </c>
+      <c r="X91">
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5299,7 +4673,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -5311,31 +4685,34 @@
         <v>-37</v>
       </c>
       <c r="G92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H92" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" t="s">
         <v>31</v>
-      </c>
-      <c r="H92" t="s">
-        <v>26</v>
-      </c>
-      <c r="I92" t="s">
-        <v>27</v>
       </c>
       <c r="J92">
         <v>7</v>
       </c>
       <c r="K92" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>29</v>
+        <v>44</v>
+      </c>
+      <c r="R92" t="s">
+        <v>33</v>
       </c>
       <c r="S92" t="s">
-        <v>30</v>
-      </c>
-      <c r="U92">
+        <v>34</v>
+      </c>
+      <c r="U92" t="s">
+        <v>35</v>
+      </c>
+      <c r="X92">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5343,7 +4720,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -5355,25 +4732,25 @@
         <v>-44</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>30</v>
-      </c>
-      <c r="U93">
+        <v>32</v>
+      </c>
+      <c r="R93" t="s">
+        <v>35</v>
+      </c>
+      <c r="X93">
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5381,7 +4758,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -5393,34 +4770,37 @@
         <v>-44</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H94" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I94" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J94">
         <v>-5</v>
       </c>
       <c r="K94" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R94" t="s">
+        <v>36</v>
       </c>
       <c r="S94" t="s">
-        <v>30</v>
-      </c>
-      <c r="T94" t="s">
-        <v>30</v>
-      </c>
-      <c r="U94">
+        <v>45</v>
+      </c>
+      <c r="U94" t="s">
+        <v>35</v>
+      </c>
+      <c r="V94" t="s">
+        <v>35</v>
+      </c>
+      <c r="X94">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5428,7 +4808,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -5440,31 +4820,34 @@
         <v>-39</v>
       </c>
       <c r="G95" t="s">
+        <v>35</v>
+      </c>
+      <c r="H95" t="s">
         <v>30</v>
       </c>
-      <c r="H95" t="s">
-        <v>26</v>
-      </c>
       <c r="I95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J95">
         <v>-5</v>
       </c>
       <c r="K95" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R95" t="s">
+        <v>36</v>
       </c>
       <c r="S95" t="s">
-        <v>31</v>
-      </c>
-      <c r="U95">
+        <v>45</v>
+      </c>
+      <c r="U95" t="s">
+        <v>36</v>
+      </c>
+      <c r="X95">
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5472,7 +4855,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -5484,31 +4867,34 @@
         <v>-34</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H96" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I96" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R96" t="s">
+        <v>33</v>
       </c>
       <c r="S96" t="s">
-        <v>31</v>
-      </c>
-      <c r="U96">
+        <v>34</v>
+      </c>
+      <c r="U96" t="s">
+        <v>36</v>
+      </c>
+      <c r="X96">
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5516,7 +4902,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -5528,22 +4914,22 @@
         <v>-34</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H97" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I97" t="s">
-        <v>35</v>
-      </c>
-      <c r="O97">
+        <v>41</v>
+      </c>
+      <c r="P97">
         <v>43</v>
       </c>
-      <c r="U97">
+      <c r="X97">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5551,7 +4937,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -5563,37 +4949,40 @@
         <v>-20</v>
       </c>
       <c r="G98" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98" t="s">
         <v>30</v>
       </c>
-      <c r="H98" t="s">
-        <v>26</v>
-      </c>
       <c r="I98" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J98">
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>38</v>
-      </c>
-      <c r="L98" t="s">
         <v>44</v>
       </c>
-      <c r="Q98" t="s">
-        <v>31</v>
+      <c r="M98" t="s">
+        <v>52</v>
       </c>
       <c r="R98" t="s">
+        <v>36</v>
+      </c>
+      <c r="S98" t="s">
         <v>45</v>
       </c>
-      <c r="S98" t="s">
-        <v>31</v>
-      </c>
-      <c r="U98">
+      <c r="T98" t="s">
+        <v>53</v>
+      </c>
+      <c r="U98" t="s">
+        <v>36</v>
+      </c>
+      <c r="X98">
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5601,7 +4990,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5613,40 +5002,43 @@
         <v>-23</v>
       </c>
       <c r="G99" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H99" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I99" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J99">
         <v>-5</v>
       </c>
       <c r="K99" t="s">
-        <v>38</v>
-      </c>
-      <c r="M99">
+        <v>44</v>
+      </c>
+      <c r="N99">
         <v>5</v>
       </c>
-      <c r="N99">
-        <v>1</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>31</v>
+      <c r="O99">
+        <v>1</v>
       </c>
       <c r="R99" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="S99" t="s">
-        <v>30</v>
-      </c>
-      <c r="U99">
+        <v>45</v>
+      </c>
+      <c r="T99" t="s">
+        <v>89</v>
+      </c>
+      <c r="U99" t="s">
+        <v>35</v>
+      </c>
+      <c r="X99">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5654,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -5666,37 +5058,40 @@
         <v>-18</v>
       </c>
       <c r="G100" t="s">
+        <v>35</v>
+      </c>
+      <c r="H100" t="s">
         <v>30</v>
       </c>
-      <c r="H100" t="s">
-        <v>26</v>
-      </c>
       <c r="I100" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J100">
         <v>4</v>
       </c>
       <c r="K100" t="s">
-        <v>38</v>
-      </c>
-      <c r="L100" t="s">
         <v>44</v>
       </c>
-      <c r="Q100" t="s">
-        <v>31</v>
+      <c r="M100" t="s">
+        <v>52</v>
       </c>
       <c r="R100" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="S100" t="s">
-        <v>30</v>
-      </c>
-      <c r="U100">
+        <v>45</v>
+      </c>
+      <c r="T100" t="s">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s">
+        <v>35</v>
+      </c>
+      <c r="X100">
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5704,7 +5099,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D101">
         <v>3</v>
@@ -5716,37 +5111,40 @@
         <v>-22</v>
       </c>
       <c r="G101" t="s">
+        <v>36</v>
+      </c>
+      <c r="H101" t="s">
+        <v>30</v>
+      </c>
+      <c r="I101" t="s">
         <v>31</v>
-      </c>
-      <c r="H101" t="s">
-        <v>26</v>
-      </c>
-      <c r="I101" t="s">
-        <v>27</v>
       </c>
       <c r="J101">
         <v>5</v>
       </c>
       <c r="K101" t="s">
-        <v>38</v>
-      </c>
-      <c r="L101" t="s">
         <v>44</v>
       </c>
-      <c r="Q101" t="s">
-        <v>30</v>
+      <c r="M101" t="s">
+        <v>52</v>
       </c>
       <c r="R101" t="s">
+        <v>35</v>
+      </c>
+      <c r="S101" t="s">
         <v>45</v>
       </c>
-      <c r="S101" t="s">
-        <v>31</v>
-      </c>
-      <c r="U101">
+      <c r="T101" t="s">
+        <v>53</v>
+      </c>
+      <c r="U101" t="s">
+        <v>36</v>
+      </c>
+      <c r="X101">
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5754,7 +5152,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D102">
         <v>4</v>
@@ -5766,28 +5164,28 @@
         <v>-27</v>
       </c>
       <c r="G102" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H102" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I102" t="s">
-        <v>77</v>
-      </c>
-      <c r="O102">
-        <v>36</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>31</v>
-      </c>
-      <c r="S102" t="s">
-        <v>31</v>
-      </c>
-      <c r="U102">
+        <v>91</v>
+      </c>
+      <c r="P102">
+        <v>36</v>
+      </c>
+      <c r="R102" t="s">
+        <v>36</v>
+      </c>
+      <c r="U102" t="s">
+        <v>36</v>
+      </c>
+      <c r="X102">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5795,7 +5193,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -5807,40 +5205,43 @@
         <v>33</v>
       </c>
       <c r="G103" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I103" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>38</v>
-      </c>
-      <c r="M103">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="N103">
         <v>3</v>
       </c>
-      <c r="Q103" t="s">
-        <v>30</v>
+      <c r="O103">
+        <v>3</v>
       </c>
       <c r="R103" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="S103" t="s">
-        <v>31</v>
-      </c>
-      <c r="U103">
+        <v>45</v>
+      </c>
+      <c r="T103" t="s">
+        <v>89</v>
+      </c>
+      <c r="U103" t="s">
+        <v>36</v>
+      </c>
+      <c r="X103">
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5848,7 +5249,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5860,37 +5261,40 @@
         <v>33</v>
       </c>
       <c r="G104" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H104" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I104" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J104">
         <v>-5</v>
       </c>
       <c r="K104" t="s">
-        <v>38</v>
-      </c>
-      <c r="L104" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="M104" t="s">
+        <v>58</v>
       </c>
       <c r="R104" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="S104" t="s">
-        <v>31</v>
-      </c>
-      <c r="U104">
+        <v>83</v>
+      </c>
+      <c r="T104" t="s">
+        <v>60</v>
+      </c>
+      <c r="U104" t="s">
+        <v>36</v>
+      </c>
+      <c r="X104">
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5898,7 +5302,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5910,37 +5314,40 @@
         <v>38</v>
       </c>
       <c r="G105" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I105" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J105">
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>38</v>
-      </c>
-      <c r="L105" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="M105" t="s">
+        <v>67</v>
       </c>
       <c r="R105" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="S105" t="s">
-        <v>30</v>
-      </c>
-      <c r="U105">
+        <v>55</v>
+      </c>
+      <c r="T105" t="s">
+        <v>79</v>
+      </c>
+      <c r="U105" t="s">
+        <v>35</v>
+      </c>
+      <c r="X105">
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5948,7 +5355,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -5960,40 +5367,43 @@
         <v>36</v>
       </c>
       <c r="G106" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I106" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J106">
         <v>-1</v>
       </c>
       <c r="K106" t="s">
-        <v>38</v>
-      </c>
-      <c r="L106" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="M106" t="s">
+        <v>50</v>
       </c>
       <c r="R106" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="S106" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="T106" t="s">
-        <v>31</v>
-      </c>
-      <c r="U106">
+        <v>60</v>
+      </c>
+      <c r="U106" t="s">
+        <v>36</v>
+      </c>
+      <c r="V106" t="s">
+        <v>36</v>
+      </c>
+      <c r="X106">
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6001,7 +5411,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D107">
         <v>4</v>
@@ -6013,19 +5423,19 @@
         <v>37</v>
       </c>
       <c r="G107" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H107" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I107" t="s">
-        <v>79</v>
-      </c>
-      <c r="U107">
+        <v>93</v>
+      </c>
+      <c r="X107">
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6033,7 +5443,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -6045,31 +5455,34 @@
         <v>-20</v>
       </c>
       <c r="G108" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I108" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J108">
         <v>-5</v>
       </c>
       <c r="K108" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R108" t="s">
+        <v>36</v>
       </c>
       <c r="S108" t="s">
-        <v>30</v>
-      </c>
-      <c r="U108">
+        <v>65</v>
+      </c>
+      <c r="U108" t="s">
+        <v>35</v>
+      </c>
+      <c r="X108">
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6077,7 +5490,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -6089,31 +5502,34 @@
         <v>-15</v>
       </c>
       <c r="G109" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I109" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J109">
         <v>4</v>
       </c>
       <c r="K109" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R109" t="s">
+        <v>36</v>
       </c>
       <c r="S109" t="s">
-        <v>30</v>
-      </c>
-      <c r="U109">
+        <v>39</v>
+      </c>
+      <c r="U109" t="s">
+        <v>35</v>
+      </c>
+      <c r="X109">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6121,7 +5537,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -6133,31 +5549,34 @@
         <v>-19</v>
       </c>
       <c r="G110" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H110" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I110" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J110">
         <v>12</v>
       </c>
       <c r="K110" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>29</v>
+        <v>44</v>
+      </c>
+      <c r="R110" t="s">
+        <v>33</v>
       </c>
       <c r="S110" t="s">
-        <v>30</v>
-      </c>
-      <c r="U110">
+        <v>34</v>
+      </c>
+      <c r="U110" t="s">
+        <v>35</v>
+      </c>
+      <c r="X110">
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6165,7 +5584,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -6177,31 +5596,34 @@
         <v>-31</v>
       </c>
       <c r="G111" t="s">
+        <v>35</v>
+      </c>
+      <c r="H111" t="s">
         <v>30</v>
       </c>
-      <c r="H111" t="s">
-        <v>26</v>
-      </c>
       <c r="I111" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J111">
         <v>3</v>
       </c>
       <c r="K111" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R111" t="s">
+        <v>33</v>
       </c>
       <c r="S111" t="s">
-        <v>30</v>
-      </c>
-      <c r="U111">
+        <v>34</v>
+      </c>
+      <c r="U111" t="s">
+        <v>35</v>
+      </c>
+      <c r="X111">
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6209,7 +5631,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -6221,31 +5643,34 @@
         <v>-34</v>
       </c>
       <c r="G112" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H112" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I112" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R112" t="s">
+        <v>36</v>
       </c>
       <c r="S112" t="s">
-        <v>30</v>
-      </c>
-      <c r="U112">
+        <v>39</v>
+      </c>
+      <c r="U112" t="s">
+        <v>35</v>
+      </c>
+      <c r="X112">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6253,7 +5678,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -6265,31 +5690,34 @@
         <v>-34</v>
       </c>
       <c r="G113" t="s">
+        <v>35</v>
+      </c>
+      <c r="H113" t="s">
         <v>30</v>
       </c>
-      <c r="H113" t="s">
-        <v>26</v>
-      </c>
       <c r="I113" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J113">
         <v>8</v>
       </c>
       <c r="K113" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="R113" t="s">
+        <v>36</v>
       </c>
       <c r="S113" t="s">
-        <v>30</v>
-      </c>
-      <c r="U113">
+        <v>39</v>
+      </c>
+      <c r="U113" t="s">
+        <v>35</v>
+      </c>
+      <c r="X113">
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6297,7 +5725,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -6309,31 +5737,34 @@
         <v>-42</v>
       </c>
       <c r="G114" t="s">
+        <v>35</v>
+      </c>
+      <c r="H114" t="s">
         <v>30</v>
       </c>
-      <c r="H114" t="s">
-        <v>26</v>
-      </c>
       <c r="I114" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J114">
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R114" t="s">
+        <v>36</v>
       </c>
       <c r="S114" t="s">
-        <v>30</v>
-      </c>
-      <c r="U114">
+        <v>39</v>
+      </c>
+      <c r="U114" t="s">
+        <v>35</v>
+      </c>
+      <c r="X114">
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6341,7 +5772,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -6353,31 +5784,34 @@
         <v>-44</v>
       </c>
       <c r="G115" t="s">
+        <v>35</v>
+      </c>
+      <c r="H115" t="s">
         <v>30</v>
       </c>
-      <c r="H115" t="s">
-        <v>26</v>
-      </c>
       <c r="I115" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J115">
         <v>33</v>
       </c>
       <c r="K115" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="R115" t="s">
+        <v>36</v>
       </c>
       <c r="S115" t="s">
-        <v>31</v>
-      </c>
-      <c r="U115">
+        <v>65</v>
+      </c>
+      <c r="U115" t="s">
+        <v>36</v>
+      </c>
+      <c r="X115">
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6385,7 +5819,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -6397,31 +5831,34 @@
         <v>23</v>
       </c>
       <c r="G116" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H116" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I116" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J116">
         <v>5</v>
       </c>
       <c r="K116" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="R116" t="s">
+        <v>36</v>
       </c>
       <c r="S116" t="s">
-        <v>30</v>
-      </c>
-      <c r="U116">
+        <v>85</v>
+      </c>
+      <c r="U116" t="s">
+        <v>35</v>
+      </c>
+      <c r="X116">
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6429,7 +5866,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -6441,31 +5878,34 @@
         <v>18</v>
       </c>
       <c r="G117" t="s">
+        <v>36</v>
+      </c>
+      <c r="H117" t="s">
+        <v>30</v>
+      </c>
+      <c r="I117" t="s">
         <v>31</v>
-      </c>
-      <c r="H117" t="s">
-        <v>26</v>
-      </c>
-      <c r="I117" t="s">
-        <v>27</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R117" t="s">
+        <v>36</v>
       </c>
       <c r="S117" t="s">
-        <v>30</v>
-      </c>
-      <c r="U117">
+        <v>85</v>
+      </c>
+      <c r="U117" t="s">
+        <v>35</v>
+      </c>
+      <c r="X117">
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6473,7 +5913,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -6485,31 +5925,34 @@
         <v>18</v>
       </c>
       <c r="G118" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H118" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I118" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J118">
         <v>18</v>
       </c>
       <c r="K118" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="R118" t="s">
+        <v>35</v>
       </c>
       <c r="S118" t="s">
-        <v>31</v>
-      </c>
-      <c r="U118">
+        <v>39</v>
+      </c>
+      <c r="U118" t="s">
+        <v>36</v>
+      </c>
+      <c r="X118">
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6517,25 +5960,25 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F119">
         <v>3</v>
       </c>
       <c r="G119" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I119" t="s">
-        <v>52</v>
-      </c>
-      <c r="U119">
+        <v>62</v>
+      </c>
+      <c r="X119">
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6543,28 +5986,28 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F120">
         <v>-40</v>
       </c>
       <c r="G120" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H120" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="I120" t="s">
-        <v>71</v>
-      </c>
-      <c r="O120">
+        <v>84</v>
+      </c>
+      <c r="P120">
         <v>50</v>
       </c>
-      <c r="P120">
+      <c r="Q120">
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6572,7 +6015,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6584,37 +6027,40 @@
         <v>-44</v>
       </c>
       <c r="G121" t="s">
+        <v>36</v>
+      </c>
+      <c r="H121" t="s">
+        <v>30</v>
+      </c>
+      <c r="I121" t="s">
         <v>31</v>
       </c>
-      <c r="H121" t="s">
-        <v>26</v>
-      </c>
-      <c r="I121" t="s">
-        <v>27</v>
-      </c>
       <c r="J121">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>38</v>
-      </c>
-      <c r="L121" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="M121" t="s">
+        <v>67</v>
       </c>
       <c r="R121" t="s">
+        <v>35</v>
+      </c>
+      <c r="S121" t="s">
         <v>45</v>
       </c>
-      <c r="S121" t="s">
-        <v>31</v>
-      </c>
-      <c r="U121">
+      <c r="T121" t="s">
+        <v>53</v>
+      </c>
+      <c r="U121" t="s">
+        <v>36</v>
+      </c>
+      <c r="X121">
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6622,7 +6068,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6634,37 +6080,40 @@
         <v>-45</v>
       </c>
       <c r="G122" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H122" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I122" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J122">
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>38</v>
-      </c>
-      <c r="L122" t="s">
         <v>44</v>
       </c>
-      <c r="Q122" t="s">
-        <v>31</v>
+      <c r="M122" t="s">
+        <v>52</v>
       </c>
       <c r="R122" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="S122" t="s">
-        <v>31</v>
-      </c>
-      <c r="U122">
+        <v>71</v>
+      </c>
+      <c r="T122" t="s">
+        <v>56</v>
+      </c>
+      <c r="U122" t="s">
+        <v>36</v>
+      </c>
+      <c r="X122">
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6672,7 +6121,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -6684,37 +6133,39 @@
         <v>-47</v>
       </c>
       <c r="G123" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H123" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I123" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>38</v>
-      </c>
-      <c r="L123" t="s">
         <v>44</v>
       </c>
-      <c r="Q123" t="s">
-        <v>30</v>
+      <c r="M123" t="s">
+        <v>52</v>
       </c>
       <c r="R123" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="S123" t="s">
-        <v>30</v>
-      </c>
-      <c r="U123">
+        <v>45</v>
+      </c>
+      <c r="T123" t="s">
+        <v>56</v>
+      </c>
+      <c r="U123" t="s">
+        <v>35</v>
+      </c>
+      <c r="X123">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Scout/johnston-vs-waukee-082826.xlsx
+++ b/Scout/johnston-vs-waukee-082826.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R265283d335384935"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R7aec17589f344d02"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -112,6 +124,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -130,6 +145,9 @@
     <t>Complete</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>TRIPS</t>
   </si>
   <si>
@@ -166,6 +184,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>STRETCH</t>
   </si>
   <si>
@@ -190,6 +211,9 @@
     <t>E-Alley</t>
   </si>
   <si>
+    <t>K TUCK G</t>
+  </si>
+  <si>
     <t>Y OFF PRO</t>
   </si>
   <si>
@@ -202,6 +226,9 @@
     <t>Good</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>Fair Catch</t>
   </si>
   <si>
@@ -220,6 +247,9 @@
     <t>MESH</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>Timeout</t>
   </si>
   <si>
@@ -293,6 +323,9 @@
   </si>
   <si>
     <t>No Good</t>
+  </si>
+  <si>
+    <t>K GUN</t>
   </si>
   <si>
     <t>Extra Pt. Block</t>
@@ -302,7 +335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y123"/>
+  <dimension ref="A1:AC123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -380,6 +413,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -389,19 +434,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +457,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -424,30 +469,33 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" t="s">
-        <v>35</v>
-      </c>
-      <c r="X3">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" t="s">
+        <v>38</v>
+      </c>
+      <c r="X3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -459,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -471,33 +519,36 @@
         <v>-22</v>
       </c>
       <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
         <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
       </c>
       <c r="J4">
         <v>-5</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" t="s">
-        <v>34</v>
-      </c>
-      <c r="U4" t="s">
-        <v>35</v>
-      </c>
-      <c r="V4" t="s">
         <v>36</v>
       </c>
-      <c r="X4">
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -509,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -521,30 +572,33 @@
         <v>-17</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>33</v>
-      </c>
-      <c r="U5" t="s">
-        <v>35</v>
-      </c>
-      <c r="V5" t="s">
         <v>36</v>
       </c>
-      <c r="X5">
+      <c r="P5" t="s">
+        <v>37</v>
+      </c>
+      <c r="W5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -556,7 +610,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -568,30 +622,33 @@
         <v>-16</v>
       </c>
       <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U6" t="s">
         <v>36</v>
       </c>
-      <c r="X6">
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="W6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -603,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -615,18 +672,18 @@
         <v>-17</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7">
+        <v>47</v>
+      </c>
+      <c r="U7">
         <v>38</v>
       </c>
-      <c r="X7">
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -638,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -650,19 +707,19 @@
         <v>-45</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N8">
         <v>11</v>
@@ -670,22 +727,25 @@
       <c r="O8">
         <v>4</v>
       </c>
-      <c r="R8" t="s">
-        <v>35</v>
-      </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" t="s">
-        <v>36</v>
-      </c>
-      <c r="V8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X8">
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="W8" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -697,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -709,19 +769,19 @@
         <v>-45</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -729,19 +789,22 @@
       <c r="O9">
         <v>1</v>
       </c>
-      <c r="R9" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" t="s">
-        <v>47</v>
-      </c>
-      <c r="T9" t="s">
-        <v>48</v>
-      </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="X9">
+      <c r="P9" t="s">
+        <v>29</v>
+      </c>
+      <c r="W9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -753,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -765,19 +828,19 @@
         <v>-49</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N10">
         <v>7</v>
@@ -785,22 +848,25 @@
       <c r="O10">
         <v>1</v>
       </c>
-      <c r="R10" t="s">
-        <v>36</v>
-      </c>
-      <c r="S10" t="s">
-        <v>47</v>
-      </c>
-      <c r="T10" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" t="s">
-        <v>35</v>
-      </c>
-      <c r="V10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X10">
+      <c r="P10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -812,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -824,39 +890,42 @@
         <v>43</v>
       </c>
       <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
         <v>35</v>
       </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
       <c r="J11">
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M11" t="s">
-        <v>50</v>
-      </c>
-      <c r="R11" t="s">
-        <v>36</v>
-      </c>
-      <c r="S11" t="s">
-        <v>47</v>
-      </c>
-      <c r="T11" t="s">
-        <v>51</v>
-      </c>
-      <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" t="s">
-        <v>35</v>
-      </c>
-      <c r="X11">
+        <v>56</v>
+      </c>
+      <c r="P11" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" t="s">
+        <v>41</v>
+      </c>
+      <c r="X11" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -868,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -880,36 +949,39 @@
         <v>41</v>
       </c>
       <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
         <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s">
-        <v>31</v>
       </c>
       <c r="J12">
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
-      </c>
-      <c r="R12" t="s">
-        <v>36</v>
-      </c>
-      <c r="S12" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" t="s">
-        <v>53</v>
-      </c>
-      <c r="U12" t="s">
-        <v>36</v>
-      </c>
-      <c r="X12">
+        <v>59</v>
+      </c>
+      <c r="P12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" t="s">
+        <v>41</v>
+      </c>
+      <c r="X12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -921,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -933,19 +1005,19 @@
         <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -953,19 +1025,22 @@
       <c r="O13">
         <v>2</v>
       </c>
-      <c r="R13" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" t="s">
-        <v>34</v>
-      </c>
-      <c r="T13" t="s">
-        <v>54</v>
-      </c>
-      <c r="U13" t="s">
-        <v>36</v>
-      </c>
-      <c r="X13">
+      <c r="P13" t="s">
+        <v>57</v>
+      </c>
+      <c r="W13" t="s">
+        <v>41</v>
+      </c>
+      <c r="X13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -977,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -989,19 +1064,19 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J14">
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N14">
         <v>24</v>
@@ -1009,19 +1084,22 @@
       <c r="O14">
         <v>8</v>
       </c>
-      <c r="R14" t="s">
-        <v>35</v>
-      </c>
-      <c r="S14" t="s">
-        <v>34</v>
-      </c>
-      <c r="T14" t="s">
-        <v>49</v>
-      </c>
-      <c r="U14" t="s">
-        <v>36</v>
-      </c>
-      <c r="X14">
+      <c r="P14" t="s">
+        <v>29</v>
+      </c>
+      <c r="W14" t="s">
+        <v>40</v>
+      </c>
+      <c r="X14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -1033,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1045,36 +1123,39 @@
         <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M15" t="s">
-        <v>52</v>
-      </c>
-      <c r="R15" t="s">
-        <v>35</v>
-      </c>
-      <c r="S15" t="s">
-        <v>55</v>
-      </c>
-      <c r="T15" t="s">
-        <v>56</v>
-      </c>
-      <c r="U15" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15">
+        <v>59</v>
+      </c>
+      <c r="P15" t="s">
+        <v>57</v>
+      </c>
+      <c r="W15" t="s">
+        <v>40</v>
+      </c>
+      <c r="X15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -1086,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1098,36 +1179,39 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>9</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>58</v>
-      </c>
-      <c r="R16" t="s">
-        <v>35</v>
-      </c>
-      <c r="S16" t="s">
-        <v>59</v>
-      </c>
-      <c r="T16" t="s">
-        <v>60</v>
-      </c>
-      <c r="U16" t="s">
-        <v>36</v>
-      </c>
-      <c r="X16">
+        <v>65</v>
+      </c>
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="W16" t="s">
+        <v>40</v>
+      </c>
+      <c r="X16" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1139,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1148,15 +1232,15 @@
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
-      </c>
-      <c r="X17">
+        <v>70</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1168,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1177,15 +1261,15 @@
         <v>-40</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
-      </c>
-      <c r="X18">
+        <v>32</v>
+      </c>
+      <c r="AB18">
         <v>2</v>
       </c>
     </row>
@@ -1197,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1209,30 +1293,33 @@
         <v>-20</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J19">
         <v>11</v>
       </c>
       <c r="K19" t="s">
+        <v>50</v>
+      </c>
+      <c r="P19" t="s">
         <v>44</v>
       </c>
-      <c r="R19" t="s">
-        <v>36</v>
-      </c>
-      <c r="S19" t="s">
-        <v>39</v>
-      </c>
-      <c r="U19" t="s">
-        <v>35</v>
-      </c>
-      <c r="X19">
+      <c r="W19" t="s">
+        <v>41</v>
+      </c>
+      <c r="X19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB19">
         <v>2</v>
       </c>
     </row>
@@ -1244,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1256,30 +1343,33 @@
         <v>-31</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" t="s">
-        <v>35</v>
-      </c>
-      <c r="S20" t="s">
-        <v>39</v>
-      </c>
-      <c r="U20" t="s">
-        <v>35</v>
-      </c>
-      <c r="X20">
+        <v>36</v>
+      </c>
+      <c r="P20" t="s">
+        <v>44</v>
+      </c>
+      <c r="W20" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1291,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1303,30 +1393,33 @@
         <v>-31</v>
       </c>
       <c r="G21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
         <v>36</v>
       </c>
-      <c r="H21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
-      <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="R21" t="s">
-        <v>35</v>
-      </c>
-      <c r="S21" t="s">
-        <v>45</v>
-      </c>
-      <c r="U21" t="s">
-        <v>36</v>
-      </c>
-      <c r="X21">
+      <c r="P21" t="s">
+        <v>71</v>
+      </c>
+      <c r="W21" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1338,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1350,33 +1443,36 @@
         <v>-33</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" t="s">
         <v>36</v>
       </c>
-      <c r="S22" t="s">
-        <v>39</v>
-      </c>
-      <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" t="s">
-        <v>35</v>
-      </c>
-      <c r="X22">
+      <c r="P22" t="s">
+        <v>57</v>
+      </c>
+      <c r="W22" t="s">
+        <v>41</v>
+      </c>
+      <c r="X22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1388,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -1400,18 +1496,18 @@
         <v>-34</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>63</v>
-      </c>
-      <c r="P23">
+        <v>72</v>
+      </c>
+      <c r="U23">
         <v>31</v>
       </c>
-      <c r="X23">
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1423,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1435,19 +1531,19 @@
         <v>-36</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N24">
         <v>14</v>
@@ -1455,22 +1551,25 @@
       <c r="O24">
         <v>5</v>
       </c>
-      <c r="Q24">
+      <c r="P24" t="s">
+        <v>57</v>
+      </c>
+      <c r="V24">
         <v>0</v>
       </c>
-      <c r="R24" t="s">
-        <v>35</v>
-      </c>
-      <c r="S24" t="s">
-        <v>45</v>
-      </c>
-      <c r="T24" t="s">
-        <v>64</v>
-      </c>
-      <c r="U24" t="s">
-        <v>36</v>
-      </c>
-      <c r="X24">
+      <c r="W24" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1482,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1494,36 +1593,39 @@
         <v>-36</v>
       </c>
       <c r="G25" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" t="s">
         <v>35</v>
-      </c>
-      <c r="H25" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" t="s">
-        <v>31</v>
       </c>
       <c r="J25">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>50</v>
-      </c>
-      <c r="R25" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" t="s">
-        <v>65</v>
-      </c>
-      <c r="T25" t="s">
-        <v>60</v>
-      </c>
-      <c r="U25" t="s">
-        <v>36</v>
-      </c>
-      <c r="X25">
+        <v>56</v>
+      </c>
+      <c r="P25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X25" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1535,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1547,30 +1649,30 @@
         <v>-49</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O26">
         <v>3</v>
       </c>
-      <c r="R26" t="s">
-        <v>36</v>
-      </c>
-      <c r="U26" t="s">
-        <v>36</v>
-      </c>
-      <c r="X26">
+      <c r="W26" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1582,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1594,19 +1696,19 @@
         <v>-49</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -1614,22 +1716,25 @@
       <c r="O27">
         <v>2</v>
       </c>
-      <c r="R27" t="s">
-        <v>35</v>
-      </c>
-      <c r="S27" t="s">
-        <v>34</v>
-      </c>
-      <c r="T27" t="s">
-        <v>66</v>
-      </c>
-      <c r="U27" t="s">
-        <v>35</v>
-      </c>
-      <c r="V27" t="s">
-        <v>35</v>
-      </c>
-      <c r="X27">
+      <c r="P27" t="s">
+        <v>57</v>
+      </c>
+      <c r="W27" t="s">
+        <v>40</v>
+      </c>
+      <c r="X27" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1641,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1653,19 +1758,19 @@
         <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J28">
         <v>9</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -1673,22 +1778,25 @@
       <c r="O28">
         <v>1</v>
       </c>
-      <c r="R28" t="s">
-        <v>36</v>
-      </c>
-      <c r="S28" t="s">
-        <v>47</v>
-      </c>
-      <c r="T28" t="s">
-        <v>49</v>
-      </c>
-      <c r="U28" t="s">
-        <v>35</v>
-      </c>
-      <c r="V28" t="s">
-        <v>35</v>
-      </c>
-      <c r="X28">
+      <c r="P28" t="s">
+        <v>29</v>
+      </c>
+      <c r="W28" t="s">
+        <v>41</v>
+      </c>
+      <c r="X28" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1700,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1712,39 +1820,42 @@
         <v>34</v>
       </c>
       <c r="G29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" t="s">
         <v>35</v>
-      </c>
-      <c r="H29" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" t="s">
-        <v>31</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M29" t="s">
-        <v>67</v>
-      </c>
-      <c r="R29" t="s">
-        <v>36</v>
-      </c>
-      <c r="S29" t="s">
-        <v>45</v>
-      </c>
-      <c r="T29" t="s">
-        <v>56</v>
-      </c>
-      <c r="U29" t="s">
-        <v>36</v>
-      </c>
-      <c r="V29" t="s">
-        <v>35</v>
-      </c>
-      <c r="X29">
+        <v>76</v>
+      </c>
+      <c r="P29" t="s">
+        <v>29</v>
+      </c>
+      <c r="W29" t="s">
+        <v>41</v>
+      </c>
+      <c r="X29" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1756,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1768,19 +1879,19 @@
         <v>29</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J30">
         <v>6</v>
       </c>
       <c r="K30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N30">
         <v>7</v>
@@ -1788,19 +1899,22 @@
       <c r="O30">
         <v>1</v>
       </c>
-      <c r="R30" t="s">
-        <v>36</v>
-      </c>
-      <c r="S30" t="s">
-        <v>45</v>
-      </c>
-      <c r="T30" t="s">
-        <v>54</v>
-      </c>
-      <c r="U30" t="s">
-        <v>35</v>
-      </c>
-      <c r="X30">
+      <c r="P30" t="s">
+        <v>29</v>
+      </c>
+      <c r="W30" t="s">
+        <v>41</v>
+      </c>
+      <c r="X30" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1812,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1824,19 +1938,19 @@
         <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H31" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N31">
         <v>11</v>
@@ -1844,19 +1958,22 @@
       <c r="O31">
         <v>5</v>
       </c>
-      <c r="R31" t="s">
-        <v>35</v>
-      </c>
-      <c r="S31" t="s">
-        <v>45</v>
-      </c>
-      <c r="T31" t="s">
-        <v>68</v>
-      </c>
-      <c r="U31" t="s">
-        <v>36</v>
-      </c>
-      <c r="X31">
+      <c r="P31" t="s">
+        <v>57</v>
+      </c>
+      <c r="W31" t="s">
+        <v>40</v>
+      </c>
+      <c r="X31" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1868,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -1880,19 +1997,19 @@
         <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H32" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J32">
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -1900,19 +2017,22 @@
       <c r="O32">
         <v>3</v>
       </c>
-      <c r="R32" t="s">
-        <v>36</v>
-      </c>
-      <c r="S32" t="s">
-        <v>47</v>
-      </c>
-      <c r="T32" t="s">
-        <v>48</v>
-      </c>
-      <c r="U32" t="s">
-        <v>36</v>
-      </c>
-      <c r="X32">
+      <c r="P32" t="s">
+        <v>57</v>
+      </c>
+      <c r="W32" t="s">
+        <v>41</v>
+      </c>
+      <c r="X32" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
     </row>
@@ -1924,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1936,39 +2056,42 @@
         <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M33" t="s">
-        <v>52</v>
-      </c>
-      <c r="R33" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" t="s">
-        <v>65</v>
-      </c>
-      <c r="T33" t="s">
-        <v>56</v>
-      </c>
-      <c r="U33" t="s">
-        <v>35</v>
-      </c>
-      <c r="V33" t="s">
-        <v>35</v>
-      </c>
-      <c r="X33">
+        <v>59</v>
+      </c>
+      <c r="P33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W33" t="s">
+        <v>40</v>
+      </c>
+      <c r="X33" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB33">
         <v>2</v>
       </c>
     </row>
@@ -1980,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1992,36 +2115,39 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M34" t="s">
+        <v>76</v>
+      </c>
+      <c r="P34" t="s">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s">
+        <v>41</v>
+      </c>
+      <c r="X34" t="s">
         <v>67</v>
       </c>
-      <c r="R34" t="s">
-        <v>36</v>
-      </c>
-      <c r="S34" t="s">
-        <v>59</v>
-      </c>
-      <c r="T34" t="s">
-        <v>56</v>
-      </c>
-      <c r="U34" t="s">
-        <v>36</v>
-      </c>
-      <c r="X34">
+      <c r="Y34" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB34">
         <v>2</v>
       </c>
     </row>
@@ -2033,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -2045,21 +2171,21 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>44</v>
-      </c>
-      <c r="R35" t="s">
-        <v>35</v>
-      </c>
-      <c r="X35">
+        <v>50</v>
+      </c>
+      <c r="W35" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB35">
         <v>2</v>
       </c>
     </row>
@@ -2071,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2083,36 +2209,39 @@
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R36" t="s">
-        <v>35</v>
-      </c>
-      <c r="S36" t="s">
-        <v>47</v>
-      </c>
-      <c r="T36" t="s">
-        <v>70</v>
-      </c>
-      <c r="U36" t="s">
-        <v>35</v>
-      </c>
-      <c r="X36">
+        <v>33</v>
+      </c>
+      <c r="P36" t="s">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s">
+        <v>40</v>
+      </c>
+      <c r="X36" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB36">
         <v>2</v>
       </c>
     </row>
@@ -2124,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -2136,39 +2265,42 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M37" t="s">
-        <v>67</v>
-      </c>
-      <c r="R37" t="s">
-        <v>36</v>
-      </c>
-      <c r="S37" t="s">
-        <v>47</v>
-      </c>
-      <c r="T37" t="s">
-        <v>56</v>
-      </c>
-      <c r="U37" t="s">
-        <v>36</v>
-      </c>
-      <c r="V37" t="s">
-        <v>35</v>
-      </c>
-      <c r="X37">
+        <v>76</v>
+      </c>
+      <c r="P37" t="s">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s">
+        <v>41</v>
+      </c>
+      <c r="X37" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB37">
         <v>2</v>
       </c>
     </row>
@@ -2180,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2189,15 +2321,15 @@
         <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H38" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I38" t="s">
-        <v>62</v>
-      </c>
-      <c r="X38">
+        <v>70</v>
+      </c>
+      <c r="AB38">
         <v>2</v>
       </c>
     </row>
@@ -2209,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2218,15 +2350,15 @@
         <v>-40</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I39" t="s">
-        <v>28</v>
-      </c>
-      <c r="X39">
+        <v>32</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2238,7 +2370,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2250,30 +2382,33 @@
         <v>-20</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J40">
         <v>-4</v>
       </c>
       <c r="K40" t="s">
-        <v>32</v>
-      </c>
-      <c r="R40" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40" t="s">
         <v>71</v>
       </c>
-      <c r="U40" t="s">
-        <v>36</v>
-      </c>
-      <c r="X40">
+      <c r="W40" t="s">
+        <v>40</v>
+      </c>
+      <c r="X40" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2285,7 +2420,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2297,30 +2432,33 @@
         <v>-16</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I41" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R41" t="s">
         <v>36</v>
       </c>
-      <c r="S41" t="s">
-        <v>45</v>
-      </c>
-      <c r="U41" t="s">
-        <v>35</v>
-      </c>
-      <c r="X41">
+      <c r="P41" t="s">
+        <v>29</v>
+      </c>
+      <c r="W41" t="s">
+        <v>41</v>
+      </c>
+      <c r="X41" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2332,7 +2470,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>3</v>
@@ -2344,30 +2482,33 @@
         <v>-16</v>
       </c>
       <c r="G42" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H42" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J42">
         <v>-4</v>
       </c>
       <c r="K42" t="s">
-        <v>32</v>
-      </c>
-      <c r="R42" t="s">
-        <v>33</v>
-      </c>
-      <c r="S42" t="s">
-        <v>34</v>
-      </c>
-      <c r="U42" t="s">
-        <v>35</v>
-      </c>
-      <c r="X42">
+        <v>36</v>
+      </c>
+      <c r="P42" t="s">
+        <v>37</v>
+      </c>
+      <c r="W42" t="s">
+        <v>38</v>
+      </c>
+      <c r="X42" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2379,7 +2520,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -2391,15 +2532,15 @@
         <v>-12</v>
       </c>
       <c r="G43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I43" t="s">
-        <v>73</v>
-      </c>
-      <c r="X43">
+        <v>83</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2411,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2423,39 +2564,42 @@
         <v>38</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M44" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q44">
+        <v>56</v>
+      </c>
+      <c r="P44" t="s">
+        <v>29</v>
+      </c>
+      <c r="V44">
         <v>0</v>
       </c>
-      <c r="R44" t="s">
-        <v>36</v>
-      </c>
-      <c r="S44" t="s">
-        <v>47</v>
-      </c>
-      <c r="T44" t="s">
+      <c r="W44" t="s">
+        <v>41</v>
+      </c>
+      <c r="X44" t="s">
         <v>53</v>
       </c>
-      <c r="U44" t="s">
-        <v>36</v>
-      </c>
-      <c r="X44">
+      <c r="Y44" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2467,7 +2611,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2479,21 +2623,24 @@
         <v>38</v>
       </c>
       <c r="G45" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I45" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>44</v>
-      </c>
-      <c r="R45" t="s">
-        <v>36</v>
-      </c>
-      <c r="X45">
+        <v>50</v>
+      </c>
+      <c r="P45" t="s">
+        <v>57</v>
+      </c>
+      <c r="W45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB45">
         <v>3</v>
       </c>
     </row>
@@ -2505,10 +2652,10 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="R46" t="s">
-        <v>36</v>
+        <v>85</v>
+      </c>
+      <c r="W46" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="47">
@@ -2519,7 +2666,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2531,33 +2678,36 @@
         <v>38</v>
       </c>
       <c r="G47" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H47" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J47">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="R47" t="s">
-        <v>35</v>
-      </c>
-      <c r="S47" t="s">
-        <v>39</v>
-      </c>
-      <c r="T47" t="s">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s">
-        <v>35</v>
-      </c>
-      <c r="X47">
+        <v>36</v>
+      </c>
+      <c r="P47" t="s">
+        <v>29</v>
+      </c>
+      <c r="W47" t="s">
+        <v>40</v>
+      </c>
+      <c r="X47" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2569,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2581,36 +2731,39 @@
         <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I48" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J48">
         <v>-3</v>
       </c>
       <c r="K48" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M48" t="s">
-        <v>67</v>
-      </c>
-      <c r="R48" t="s">
-        <v>36</v>
-      </c>
-      <c r="S48" t="s">
-        <v>39</v>
-      </c>
-      <c r="T48" t="s">
-        <v>54</v>
-      </c>
-      <c r="U48" t="s">
-        <v>36</v>
-      </c>
-      <c r="X48">
+        <v>76</v>
+      </c>
+      <c r="P48" t="s">
+        <v>57</v>
+      </c>
+      <c r="W48" t="s">
+        <v>41</v>
+      </c>
+      <c r="X48" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -2622,7 +2775,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2634,19 +2787,19 @@
         <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N49">
         <v>32</v>
@@ -2654,19 +2807,22 @@
       <c r="O49">
         <v>7</v>
       </c>
-      <c r="R49" t="s">
-        <v>36</v>
-      </c>
-      <c r="S49" t="s">
-        <v>45</v>
-      </c>
-      <c r="T49" t="s">
-        <v>49</v>
-      </c>
-      <c r="U49" t="s">
-        <v>35</v>
-      </c>
-      <c r="X49">
+      <c r="P49" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" t="s">
+        <v>41</v>
+      </c>
+      <c r="X49" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2678,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2690,27 +2846,30 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I50" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J50">
         <v>-5</v>
       </c>
       <c r="K50" t="s">
-        <v>44</v>
-      </c>
-      <c r="R50" t="s">
-        <v>36</v>
-      </c>
-      <c r="S50" t="s">
-        <v>45</v>
-      </c>
-      <c r="V50" t="s">
-        <v>35</v>
-      </c>
-      <c r="X50">
+        <v>50</v>
+      </c>
+      <c r="P50" t="s">
+        <v>29</v>
+      </c>
+      <c r="W50" t="s">
+        <v>41</v>
+      </c>
+      <c r="X50" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2722,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2734,19 +2893,19 @@
         <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H51" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J51">
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N51">
         <v>6</v>
@@ -2754,19 +2913,22 @@
       <c r="O51">
         <v>2</v>
       </c>
-      <c r="R51" t="s">
-        <v>36</v>
-      </c>
-      <c r="S51" t="s">
-        <v>45</v>
-      </c>
-      <c r="T51" t="s">
-        <v>64</v>
-      </c>
-      <c r="U51" t="s">
-        <v>35</v>
-      </c>
-      <c r="X51">
+      <c r="P51" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" t="s">
+        <v>41</v>
+      </c>
+      <c r="X51" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2778,7 +2940,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -2790,36 +2952,39 @@
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J52">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M52" t="s">
-        <v>52</v>
-      </c>
-      <c r="R52" t="s">
-        <v>35</v>
-      </c>
-      <c r="S52" t="s">
-        <v>55</v>
-      </c>
-      <c r="T52" t="s">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s">
-        <v>36</v>
-      </c>
-      <c r="X52">
+        <v>59</v>
+      </c>
+      <c r="P52" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" t="s">
+        <v>40</v>
+      </c>
+      <c r="X52" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB52">
         <v>3</v>
       </c>
     </row>
@@ -2831,7 +2996,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -2843,36 +3008,39 @@
         <v>5</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J53">
         <v>3</v>
       </c>
       <c r="K53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M53" t="s">
-        <v>52</v>
-      </c>
-      <c r="R53" t="s">
-        <v>36</v>
-      </c>
-      <c r="S53" t="s">
         <v>59</v>
       </c>
-      <c r="T53" t="s">
-        <v>79</v>
-      </c>
-      <c r="U53" t="s">
-        <v>35</v>
-      </c>
-      <c r="X53">
+      <c r="P53" t="s">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s">
+        <v>41</v>
+      </c>
+      <c r="X53" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB53">
         <v>3</v>
       </c>
     </row>
@@ -2884,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2896,39 +3064,42 @@
         <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J54">
         <v>-1</v>
       </c>
       <c r="K54" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M54" t="s">
-        <v>67</v>
-      </c>
-      <c r="R54" t="s">
-        <v>36</v>
-      </c>
-      <c r="S54" t="s">
-        <v>47</v>
-      </c>
-      <c r="T54" t="s">
-        <v>79</v>
-      </c>
-      <c r="U54" t="s">
-        <v>36</v>
-      </c>
-      <c r="V54" t="s">
-        <v>35</v>
-      </c>
-      <c r="X54">
+        <v>76</v>
+      </c>
+      <c r="P54" t="s">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s">
+        <v>41</v>
+      </c>
+      <c r="X54" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB54">
         <v>3</v>
       </c>
     </row>
@@ -2940,7 +3111,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2952,36 +3123,39 @@
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J55">
         <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M55" t="s">
-        <v>58</v>
-      </c>
-      <c r="R55" t="s">
-        <v>36</v>
-      </c>
-      <c r="S55" t="s">
-        <v>47</v>
-      </c>
-      <c r="T55" t="s">
-        <v>80</v>
-      </c>
-      <c r="U55" t="s">
-        <v>35</v>
-      </c>
-      <c r="X55">
+        <v>65</v>
+      </c>
+      <c r="P55" t="s">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s">
+        <v>41</v>
+      </c>
+      <c r="X55" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB55">
         <v>3</v>
       </c>
     </row>
@@ -2993,7 +3167,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -3005,15 +3179,15 @@
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I56" t="s">
-        <v>62</v>
-      </c>
-      <c r="X56">
+        <v>70</v>
+      </c>
+      <c r="AB56">
         <v>3</v>
       </c>
     </row>
@@ -3025,19 +3199,19 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F57">
         <v>-40</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I57" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
@@ -3048,7 +3222,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3060,30 +3234,33 @@
         <v>-20</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H58" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J58">
         <v>-6</v>
       </c>
       <c r="K58" t="s">
-        <v>32</v>
-      </c>
-      <c r="R58" t="s">
-        <v>33</v>
-      </c>
-      <c r="S58" t="s">
-        <v>34</v>
-      </c>
-      <c r="U58" t="s">
-        <v>35</v>
-      </c>
-      <c r="X58">
+        <v>36</v>
+      </c>
+      <c r="P58" t="s">
+        <v>37</v>
+      </c>
+      <c r="W58" t="s">
+        <v>38</v>
+      </c>
+      <c r="X58" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
     </row>
@@ -3095,7 +3272,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3107,39 +3284,42 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H59" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I59" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J59">
         <v>-10</v>
       </c>
       <c r="K59" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M59" t="s">
-        <v>50</v>
-      </c>
-      <c r="R59" t="s">
-        <v>35</v>
-      </c>
-      <c r="S59" t="s">
-        <v>71</v>
-      </c>
-      <c r="T59" t="s">
-        <v>82</v>
-      </c>
-      <c r="U59" t="s">
-        <v>35</v>
-      </c>
-      <c r="V59" t="s">
-        <v>35</v>
-      </c>
-      <c r="X59">
+        <v>56</v>
+      </c>
+      <c r="P59" t="s">
+        <v>29</v>
+      </c>
+      <c r="W59" t="s">
+        <v>40</v>
+      </c>
+      <c r="X59" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -3151,7 +3331,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3163,19 +3343,19 @@
         <v>24</v>
       </c>
       <c r="G60" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H60" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N60">
         <v>24</v>
@@ -3183,19 +3363,22 @@
       <c r="O60">
         <v>4</v>
       </c>
-      <c r="R60" t="s">
-        <v>35</v>
-      </c>
-      <c r="S60" t="s">
-        <v>71</v>
-      </c>
-      <c r="T60" t="s">
-        <v>77</v>
-      </c>
-      <c r="U60" t="s">
-        <v>35</v>
-      </c>
-      <c r="X60">
+      <c r="P60" t="s">
+        <v>57</v>
+      </c>
+      <c r="W60" t="s">
+        <v>40</v>
+      </c>
+      <c r="X60" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -3207,7 +3390,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -3219,39 +3402,42 @@
         <v>5</v>
       </c>
       <c r="G61" t="s">
+        <v>40</v>
+      </c>
+      <c r="H61" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" t="s">
         <v>35</v>
-      </c>
-      <c r="H61" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" t="s">
-        <v>31</v>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M61" t="s">
-        <v>50</v>
-      </c>
-      <c r="R61" t="s">
-        <v>36</v>
-      </c>
-      <c r="S61" t="s">
-        <v>83</v>
-      </c>
-      <c r="T61" t="s">
-        <v>51</v>
-      </c>
-      <c r="U61" t="s">
-        <v>36</v>
-      </c>
-      <c r="V61" t="s">
-        <v>36</v>
-      </c>
-      <c r="X61">
+        <v>56</v>
+      </c>
+      <c r="P61" t="s">
+        <v>29</v>
+      </c>
+      <c r="W61" t="s">
+        <v>41</v>
+      </c>
+      <c r="X61" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -3263,7 +3449,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3275,36 +3461,39 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
+        <v>41</v>
+      </c>
+      <c r="H62" t="s">
+        <v>34</v>
+      </c>
+      <c r="I62" t="s">
+        <v>64</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
         <v>36</v>
       </c>
-      <c r="H62" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" t="s">
-        <v>57</v>
-      </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
-      <c r="K62" t="s">
-        <v>32</v>
-      </c>
       <c r="M62" t="s">
+        <v>76</v>
+      </c>
+      <c r="P62" t="s">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s">
+        <v>41</v>
+      </c>
+      <c r="X62" t="s">
         <v>67</v>
       </c>
-      <c r="R62" t="s">
-        <v>36</v>
-      </c>
-      <c r="S62" t="s">
-        <v>59</v>
-      </c>
-      <c r="T62" t="s">
-        <v>56</v>
-      </c>
-      <c r="U62" t="s">
-        <v>36</v>
-      </c>
-      <c r="X62">
+      <c r="Y62" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB62">
         <v>4</v>
       </c>
     </row>
@@ -3316,7 +3505,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -3328,18 +3517,18 @@
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I63" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
-      <c r="X63">
+      <c r="AB63">
         <v>4</v>
       </c>
     </row>
@@ -3351,7 +3540,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3360,21 +3549,21 @@
         <v>-40</v>
       </c>
       <c r="G64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I64" t="s">
-        <v>84</v>
-      </c>
-      <c r="P64">
+        <v>94</v>
+      </c>
+      <c r="U64">
         <v>56</v>
       </c>
-      <c r="Q64">
+      <c r="V64">
         <v>63</v>
       </c>
-      <c r="X64">
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3386,7 +3575,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3398,33 +3587,36 @@
         <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>32</v>
-      </c>
-      <c r="R65" t="s">
         <v>36</v>
       </c>
-      <c r="S65" t="s">
-        <v>85</v>
-      </c>
-      <c r="U65" t="s">
-        <v>35</v>
-      </c>
-      <c r="V65" t="s">
-        <v>36</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>44</v>
+      </c>
+      <c r="W65" t="s">
+        <v>41</v>
+      </c>
+      <c r="X65" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB65">
         <v>5</v>
       </c>
     </row>
@@ -3436,7 +3628,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3448,30 +3640,33 @@
         <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J66">
         <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>44</v>
-      </c>
-      <c r="R66" t="s">
-        <v>35</v>
-      </c>
-      <c r="S66" t="s">
-        <v>45</v>
-      </c>
-      <c r="U66" t="s">
-        <v>36</v>
-      </c>
-      <c r="X66">
+        <v>50</v>
+      </c>
+      <c r="P66" t="s">
+        <v>57</v>
+      </c>
+      <c r="W66" t="s">
+        <v>40</v>
+      </c>
+      <c r="X66" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3483,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -3495,33 +3690,36 @@
         <v>24</v>
       </c>
       <c r="G67" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H67" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>32</v>
-      </c>
-      <c r="R67" t="s">
-        <v>35</v>
-      </c>
-      <c r="S67" t="s">
-        <v>45</v>
-      </c>
-      <c r="U67" t="s">
-        <v>35</v>
-      </c>
-      <c r="V67" t="s">
-        <v>35</v>
-      </c>
-      <c r="X67">
+        <v>36</v>
+      </c>
+      <c r="P67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W67" t="s">
+        <v>40</v>
+      </c>
+      <c r="X67" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3533,7 +3731,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3545,18 +3743,18 @@
         <v>24</v>
       </c>
       <c r="G68" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I68" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>32</v>
-      </c>
-      <c r="X68">
+        <v>36</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3568,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>4</v>
@@ -3580,30 +3778,33 @@
         <v>24</v>
       </c>
       <c r="G69" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H69" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>32</v>
-      </c>
-      <c r="R69" t="s">
         <v>36</v>
       </c>
-      <c r="S69" t="s">
-        <v>85</v>
-      </c>
-      <c r="U69" t="s">
-        <v>36</v>
-      </c>
-      <c r="X69">
+      <c r="P69" t="s">
+        <v>71</v>
+      </c>
+      <c r="W69" t="s">
+        <v>41</v>
+      </c>
+      <c r="X69" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3615,7 +3816,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3627,19 +3828,19 @@
         <v>-23</v>
       </c>
       <c r="G70" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H70" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -3647,19 +3848,22 @@
       <c r="O70">
         <v>3</v>
       </c>
-      <c r="R70" t="s">
-        <v>35</v>
-      </c>
-      <c r="S70" t="s">
-        <v>71</v>
-      </c>
-      <c r="T70" t="s">
-        <v>64</v>
-      </c>
-      <c r="U70" t="s">
-        <v>36</v>
-      </c>
-      <c r="X70">
+      <c r="P70" t="s">
+        <v>57</v>
+      </c>
+      <c r="W70" t="s">
+        <v>40</v>
+      </c>
+      <c r="X70" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3671,7 +3875,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -3683,19 +3887,19 @@
         <v>-23</v>
       </c>
       <c r="G71" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J71">
         <v>19</v>
       </c>
       <c r="K71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N71">
         <v>16</v>
@@ -3703,19 +3907,22 @@
       <c r="O71">
         <v>3</v>
       </c>
-      <c r="R71" t="s">
-        <v>35</v>
-      </c>
-      <c r="S71" t="s">
-        <v>45</v>
-      </c>
-      <c r="T71" t="s">
-        <v>46</v>
-      </c>
-      <c r="U71" t="s">
-        <v>36</v>
-      </c>
-      <c r="X71">
+      <c r="P71" t="s">
+        <v>29</v>
+      </c>
+      <c r="W71" t="s">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3727,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3739,33 +3946,36 @@
         <v>-42</v>
       </c>
       <c r="G72" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H72" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J72">
         <v>-8</v>
       </c>
       <c r="K72" t="s">
-        <v>44</v>
-      </c>
-      <c r="R72" t="s">
-        <v>35</v>
-      </c>
-      <c r="S72" t="s">
-        <v>45</v>
-      </c>
-      <c r="T72" t="s">
-        <v>64</v>
-      </c>
-      <c r="U72" t="s">
-        <v>36</v>
-      </c>
-      <c r="X72">
+        <v>50</v>
+      </c>
+      <c r="P72" t="s">
+        <v>29</v>
+      </c>
+      <c r="W72" t="s">
+        <v>40</v>
+      </c>
+      <c r="X72" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB72">
         <v>5</v>
       </c>
     </row>
@@ -3777,7 +3987,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -3789,24 +3999,27 @@
         <v>-34</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I73" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J73">
         <v>5</v>
       </c>
       <c r="K73" t="s">
-        <v>44</v>
-      </c>
-      <c r="R73" t="s">
-        <v>35</v>
-      </c>
-      <c r="S73" t="s">
-        <v>45</v>
-      </c>
-      <c r="X73">
+        <v>50</v>
+      </c>
+      <c r="P73" t="s">
+        <v>29</v>
+      </c>
+      <c r="W73" t="s">
+        <v>40</v>
+      </c>
+      <c r="X73" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB73">
         <v>5</v>
       </c>
     </row>
@@ -3818,7 +4031,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3830,19 +4043,19 @@
         <v>-39</v>
       </c>
       <c r="G74" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H74" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J74">
         <v>28</v>
       </c>
       <c r="K74" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N74">
         <v>25</v>
@@ -3850,22 +4063,25 @@
       <c r="O74">
         <v>8</v>
       </c>
-      <c r="R74" t="s">
-        <v>35</v>
-      </c>
-      <c r="S74" t="s">
-        <v>45</v>
-      </c>
-      <c r="T74" t="s">
-        <v>49</v>
-      </c>
-      <c r="U74" t="s">
-        <v>35</v>
-      </c>
-      <c r="V74" t="s">
-        <v>36</v>
-      </c>
-      <c r="X74">
+      <c r="P74" t="s">
+        <v>57</v>
+      </c>
+      <c r="W74" t="s">
+        <v>40</v>
+      </c>
+      <c r="X74" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -3877,7 +4093,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3889,36 +4105,39 @@
         <v>33</v>
       </c>
       <c r="G75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H75" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J75">
         <v>4</v>
       </c>
       <c r="K75" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N75">
         <v>0</v>
       </c>
-      <c r="R75" t="s">
-        <v>35</v>
-      </c>
-      <c r="S75" t="s">
-        <v>45</v>
-      </c>
-      <c r="T75" t="s">
-        <v>66</v>
-      </c>
-      <c r="U75" t="s">
-        <v>35</v>
-      </c>
-      <c r="X75">
+      <c r="P75" t="s">
+        <v>29</v>
+      </c>
+      <c r="W75" t="s">
+        <v>40</v>
+      </c>
+      <c r="X75" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -3930,7 +4149,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3942,19 +4161,19 @@
         <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H76" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J76">
         <v>29</v>
       </c>
       <c r="K76" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N76">
         <v>19</v>
@@ -3962,19 +4181,22 @@
       <c r="O76">
         <v>8</v>
       </c>
-      <c r="R76" t="s">
-        <v>36</v>
-      </c>
-      <c r="S76" t="s">
-        <v>45</v>
-      </c>
-      <c r="T76" t="s">
-        <v>49</v>
-      </c>
-      <c r="U76" t="s">
-        <v>35</v>
-      </c>
-      <c r="X76">
+      <c r="P76" t="s">
+        <v>57</v>
+      </c>
+      <c r="W76" t="s">
+        <v>41</v>
+      </c>
+      <c r="X76" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -3986,7 +4208,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3998,15 +4220,15 @@
         <v>3</v>
       </c>
       <c r="G77" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H77" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I77" t="s">
-        <v>62</v>
-      </c>
-      <c r="X77">
+        <v>70</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -4018,7 +4240,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4027,15 +4249,15 @@
         <v>-40</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I78" t="s">
-        <v>84</v>
-      </c>
-      <c r="X78">
+        <v>94</v>
+      </c>
+      <c r="AB78">
         <v>6</v>
       </c>
     </row>
@@ -4047,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -4059,30 +4281,33 @@
         <v>-20</v>
       </c>
       <c r="G79" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J79">
         <v>20</v>
       </c>
       <c r="K79" t="s">
-        <v>44</v>
-      </c>
-      <c r="R79" t="s">
-        <v>36</v>
-      </c>
-      <c r="S79" t="s">
-        <v>71</v>
-      </c>
-      <c r="U79" t="s">
-        <v>35</v>
-      </c>
-      <c r="X79">
+        <v>50</v>
+      </c>
+      <c r="P79" t="s">
+        <v>57</v>
+      </c>
+      <c r="W79" t="s">
+        <v>41</v>
+      </c>
+      <c r="X79" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB79">
         <v>6</v>
       </c>
     </row>
@@ -4094,27 +4319,27 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F80">
         <v>-40</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I80" t="s">
-        <v>84</v>
-      </c>
-      <c r="P80">
+        <v>94</v>
+      </c>
+      <c r="U80">
         <v>57</v>
       </c>
-      <c r="Q80">
-        <v>40</v>
-      </c>
-      <c r="X80">
+      <c r="V80">
+        <v>40</v>
+      </c>
+      <c r="AB80">
         <v>7</v>
       </c>
     </row>
@@ -4126,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4138,36 +4363,39 @@
         <v>-43</v>
       </c>
       <c r="G81" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J81">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M81" t="s">
-        <v>67</v>
-      </c>
-      <c r="R81" t="s">
-        <v>36</v>
-      </c>
-      <c r="S81" t="s">
-        <v>71</v>
-      </c>
-      <c r="T81" t="s">
-        <v>56</v>
-      </c>
-      <c r="U81" t="s">
-        <v>36</v>
-      </c>
-      <c r="X81">
+        <v>76</v>
+      </c>
+      <c r="P81" t="s">
+        <v>29</v>
+      </c>
+      <c r="W81" t="s">
+        <v>41</v>
+      </c>
+      <c r="X81" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB81">
         <v>5</v>
       </c>
     </row>
@@ -4179,7 +4407,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -4191,19 +4419,19 @@
         <v>-44</v>
       </c>
       <c r="G82" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H82" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J82">
         <v>-3</v>
       </c>
       <c r="K82" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N82">
         <v>0</v>
@@ -4211,22 +4439,25 @@
       <c r="O82">
         <v>3</v>
       </c>
-      <c r="R82" t="s">
-        <v>36</v>
-      </c>
-      <c r="S82" t="s">
-        <v>71</v>
-      </c>
-      <c r="T82" t="s">
-        <v>66</v>
-      </c>
-      <c r="U82" t="s">
-        <v>36</v>
-      </c>
-      <c r="V82" t="s">
-        <v>35</v>
-      </c>
-      <c r="X82">
+      <c r="P82" t="s">
+        <v>29</v>
+      </c>
+      <c r="W82" t="s">
+        <v>41</v>
+      </c>
+      <c r="X82" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82">
         <v>5</v>
       </c>
     </row>
@@ -4238,7 +4469,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -4250,33 +4481,36 @@
         <v>-41</v>
       </c>
       <c r="G83" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J83">
         <v>5</v>
       </c>
       <c r="K83" t="s">
-        <v>44</v>
-      </c>
-      <c r="R83" t="s">
-        <v>35</v>
-      </c>
-      <c r="S83" t="s">
-        <v>45</v>
-      </c>
-      <c r="T83" t="s">
-        <v>49</v>
-      </c>
-      <c r="U83" t="s">
-        <v>36</v>
-      </c>
-      <c r="X83">
+        <v>50</v>
+      </c>
+      <c r="P83" t="s">
+        <v>57</v>
+      </c>
+      <c r="W83" t="s">
+        <v>40</v>
+      </c>
+      <c r="X83" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB83">
         <v>5</v>
       </c>
     </row>
@@ -4288,7 +4522,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -4300,19 +4534,19 @@
         <v>-36</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J84">
         <v>23</v>
       </c>
       <c r="K84" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N84">
         <v>14</v>
@@ -4320,19 +4554,22 @@
       <c r="O84">
         <v>5</v>
       </c>
-      <c r="R84" t="s">
-        <v>35</v>
-      </c>
-      <c r="S84" t="s">
-        <v>45</v>
-      </c>
-      <c r="T84" t="s">
-        <v>49</v>
-      </c>
-      <c r="U84" t="s">
-        <v>35</v>
-      </c>
-      <c r="X84">
+      <c r="P84" t="s">
+        <v>57</v>
+      </c>
+      <c r="W84" t="s">
+        <v>40</v>
+      </c>
+      <c r="X84" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB84">
         <v>5</v>
       </c>
     </row>
@@ -4344,7 +4581,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -4356,36 +4593,39 @@
         <v>41</v>
       </c>
       <c r="G85" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I85" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J85">
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M85" t="s">
-        <v>50</v>
-      </c>
-      <c r="R85" t="s">
-        <v>35</v>
-      </c>
-      <c r="S85" t="s">
-        <v>83</v>
-      </c>
-      <c r="T85" t="s">
-        <v>60</v>
-      </c>
-      <c r="U85" t="s">
-        <v>36</v>
-      </c>
-      <c r="X85">
+        <v>56</v>
+      </c>
+      <c r="P85" t="s">
+        <v>57</v>
+      </c>
+      <c r="W85" t="s">
+        <v>40</v>
+      </c>
+      <c r="X85" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB85">
         <v>5</v>
       </c>
     </row>
@@ -4397,7 +4637,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -4409,19 +4649,19 @@
         <v>39</v>
       </c>
       <c r="G86" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H86" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N86">
         <v>26</v>
@@ -4429,19 +4669,22 @@
       <c r="O86">
         <v>9</v>
       </c>
-      <c r="R86" t="s">
-        <v>35</v>
-      </c>
-      <c r="S86" t="s">
-        <v>55</v>
-      </c>
-      <c r="T86" t="s">
-        <v>88</v>
-      </c>
-      <c r="U86" t="s">
-        <v>36</v>
-      </c>
-      <c r="X86">
+      <c r="P86" t="s">
+        <v>57</v>
+      </c>
+      <c r="W86" t="s">
+        <v>40</v>
+      </c>
+      <c r="X86" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB86">
         <v>5</v>
       </c>
     </row>
@@ -4453,7 +4696,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -4465,19 +4708,19 @@
         <v>39</v>
       </c>
       <c r="G87" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H87" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J87">
         <v>39</v>
       </c>
       <c r="K87" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N87">
         <v>34</v>
@@ -4485,19 +4728,22 @@
       <c r="O87">
         <v>9</v>
       </c>
-      <c r="R87" t="s">
-        <v>35</v>
-      </c>
-      <c r="S87" t="s">
-        <v>45</v>
-      </c>
-      <c r="T87" t="s">
-        <v>64</v>
-      </c>
-      <c r="U87" t="s">
-        <v>36</v>
-      </c>
-      <c r="X87">
+      <c r="P87" t="s">
+        <v>29</v>
+      </c>
+      <c r="W87" t="s">
+        <v>40</v>
+      </c>
+      <c r="X87" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB87">
         <v>5</v>
       </c>
     </row>
@@ -4509,7 +4755,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4518,18 +4764,18 @@
         <v>3</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I88" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J88">
         <v>3</v>
       </c>
-      <c r="X88">
+      <c r="AB88">
         <v>5</v>
       </c>
     </row>
@@ -4541,7 +4787,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -4553,21 +4799,21 @@
         <v>-40</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H89" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P89">
+        <v>94</v>
+      </c>
+      <c r="U89">
         <v>59</v>
       </c>
-      <c r="Q89">
+      <c r="V89">
         <v>20</v>
       </c>
-      <c r="X89">
+      <c r="AB89">
         <v>6</v>
       </c>
     </row>
@@ -4579,7 +4825,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4591,30 +4837,33 @@
         <v>-10</v>
       </c>
       <c r="G90" t="s">
+        <v>40</v>
+      </c>
+      <c r="H90" t="s">
+        <v>34</v>
+      </c>
+      <c r="I90" t="s">
         <v>35</v>
       </c>
-      <c r="H90" t="s">
-        <v>30</v>
-      </c>
-      <c r="I90" t="s">
-        <v>31</v>
-      </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>32</v>
-      </c>
-      <c r="R90" t="s">
         <v>36</v>
       </c>
-      <c r="S90" t="s">
-        <v>71</v>
-      </c>
-      <c r="U90" t="s">
-        <v>36</v>
-      </c>
-      <c r="X90">
+      <c r="P90" t="s">
+        <v>57</v>
+      </c>
+      <c r="W90" t="s">
+        <v>41</v>
+      </c>
+      <c r="X90" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB90">
         <v>7</v>
       </c>
     </row>
@@ -4626,7 +4875,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -4638,30 +4887,33 @@
         <v>-13</v>
       </c>
       <c r="G91" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J91">
         <v>24</v>
       </c>
       <c r="K91" t="s">
-        <v>44</v>
-      </c>
-      <c r="R91" t="s">
-        <v>33</v>
-      </c>
-      <c r="S91" t="s">
-        <v>34</v>
-      </c>
-      <c r="U91" t="s">
-        <v>36</v>
-      </c>
-      <c r="X91">
+        <v>50</v>
+      </c>
+      <c r="P91" t="s">
+        <v>37</v>
+      </c>
+      <c r="W91" t="s">
+        <v>38</v>
+      </c>
+      <c r="X91" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB91">
         <v>7</v>
       </c>
     </row>
@@ -4673,7 +4925,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4685,30 +4937,33 @@
         <v>-37</v>
       </c>
       <c r="G92" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I92" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J92">
         <v>7</v>
       </c>
       <c r="K92" t="s">
-        <v>44</v>
-      </c>
-      <c r="R92" t="s">
-        <v>33</v>
-      </c>
-      <c r="S92" t="s">
-        <v>34</v>
-      </c>
-      <c r="U92" t="s">
-        <v>35</v>
-      </c>
-      <c r="X92">
+        <v>50</v>
+      </c>
+      <c r="P92" t="s">
+        <v>37</v>
+      </c>
+      <c r="W92" t="s">
+        <v>38</v>
+      </c>
+      <c r="X92" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB92">
         <v>7</v>
       </c>
     </row>
@@ -4720,7 +4975,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -4732,21 +4987,21 @@
         <v>-44</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I93" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>32</v>
-      </c>
-      <c r="R93" t="s">
-        <v>35</v>
-      </c>
-      <c r="X93">
+        <v>36</v>
+      </c>
+      <c r="W93" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB93">
         <v>7</v>
       </c>
     </row>
@@ -4758,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -4770,33 +5025,36 @@
         <v>-44</v>
       </c>
       <c r="G94" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H94" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J94">
         <v>-5</v>
       </c>
       <c r="K94" t="s">
-        <v>32</v>
-      </c>
-      <c r="R94" t="s">
         <v>36</v>
       </c>
-      <c r="S94" t="s">
-        <v>45</v>
-      </c>
-      <c r="U94" t="s">
-        <v>35</v>
-      </c>
-      <c r="V94" t="s">
-        <v>35</v>
-      </c>
-      <c r="X94">
+      <c r="P94" t="s">
+        <v>71</v>
+      </c>
+      <c r="W94" t="s">
+        <v>41</v>
+      </c>
+      <c r="X94" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94">
         <v>7</v>
       </c>
     </row>
@@ -4808,7 +5066,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -4820,30 +5078,33 @@
         <v>-39</v>
       </c>
       <c r="G95" t="s">
+        <v>40</v>
+      </c>
+      <c r="H95" t="s">
+        <v>34</v>
+      </c>
+      <c r="I95" t="s">
         <v>35</v>
-      </c>
-      <c r="H95" t="s">
-        <v>30</v>
-      </c>
-      <c r="I95" t="s">
-        <v>31</v>
       </c>
       <c r="J95">
         <v>-5</v>
       </c>
       <c r="K95" t="s">
-        <v>32</v>
-      </c>
-      <c r="R95" t="s">
         <v>36</v>
       </c>
-      <c r="S95" t="s">
-        <v>45</v>
-      </c>
-      <c r="U95" t="s">
-        <v>36</v>
-      </c>
-      <c r="X95">
+      <c r="P95" t="s">
+        <v>57</v>
+      </c>
+      <c r="W95" t="s">
+        <v>41</v>
+      </c>
+      <c r="X95" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB95">
         <v>7</v>
       </c>
     </row>
@@ -4855,7 +5116,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -4867,30 +5128,33 @@
         <v>-34</v>
       </c>
       <c r="G96" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>32</v>
-      </c>
-      <c r="R96" t="s">
-        <v>33</v>
-      </c>
-      <c r="S96" t="s">
-        <v>34</v>
-      </c>
-      <c r="U96" t="s">
         <v>36</v>
       </c>
-      <c r="X96">
+      <c r="P96" t="s">
+        <v>37</v>
+      </c>
+      <c r="W96" t="s">
+        <v>38</v>
+      </c>
+      <c r="X96" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB96">
         <v>7</v>
       </c>
     </row>
@@ -4902,7 +5166,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -4914,18 +5178,18 @@
         <v>-34</v>
       </c>
       <c r="G97" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H97" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>41</v>
-      </c>
-      <c r="P97">
+        <v>47</v>
+      </c>
+      <c r="U97">
         <v>43</v>
       </c>
-      <c r="X97">
+      <c r="AB97">
         <v>7</v>
       </c>
     </row>
@@ -4937,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -4949,36 +5213,39 @@
         <v>-20</v>
       </c>
       <c r="G98" t="s">
+        <v>40</v>
+      </c>
+      <c r="H98" t="s">
+        <v>34</v>
+      </c>
+      <c r="I98" t="s">
         <v>35</v>
       </c>
-      <c r="H98" t="s">
-        <v>30</v>
-      </c>
-      <c r="I98" t="s">
-        <v>31</v>
-      </c>
       <c r="J98">
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M98" t="s">
-        <v>52</v>
-      </c>
-      <c r="R98" t="s">
-        <v>36</v>
-      </c>
-      <c r="S98" t="s">
-        <v>45</v>
-      </c>
-      <c r="T98" t="s">
-        <v>53</v>
-      </c>
-      <c r="U98" t="s">
-        <v>36</v>
-      </c>
-      <c r="X98">
+        <v>59</v>
+      </c>
+      <c r="P98" t="s">
+        <v>29</v>
+      </c>
+      <c r="W98" t="s">
+        <v>41</v>
+      </c>
+      <c r="X98" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB98">
         <v>6</v>
       </c>
     </row>
@@ -4990,7 +5257,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5002,19 +5269,19 @@
         <v>-23</v>
       </c>
       <c r="G99" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H99" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J99">
         <v>-5</v>
       </c>
       <c r="K99" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N99">
         <v>5</v>
@@ -5022,19 +5289,22 @@
       <c r="O99">
         <v>1</v>
       </c>
-      <c r="R99" t="s">
-        <v>36</v>
-      </c>
-      <c r="S99" t="s">
-        <v>45</v>
-      </c>
-      <c r="T99" t="s">
-        <v>89</v>
-      </c>
-      <c r="U99" t="s">
-        <v>35</v>
-      </c>
-      <c r="X99">
+      <c r="P99" t="s">
+        <v>57</v>
+      </c>
+      <c r="W99" t="s">
+        <v>41</v>
+      </c>
+      <c r="X99" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB99">
         <v>6</v>
       </c>
     </row>
@@ -5046,7 +5316,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -5058,36 +5328,39 @@
         <v>-18</v>
       </c>
       <c r="G100" t="s">
+        <v>40</v>
+      </c>
+      <c r="H100" t="s">
+        <v>34</v>
+      </c>
+      <c r="I100" t="s">
         <v>35</v>
-      </c>
-      <c r="H100" t="s">
-        <v>30</v>
-      </c>
-      <c r="I100" t="s">
-        <v>31</v>
       </c>
       <c r="J100">
         <v>4</v>
       </c>
       <c r="K100" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M100" t="s">
-        <v>52</v>
-      </c>
-      <c r="R100" t="s">
-        <v>36</v>
-      </c>
-      <c r="S100" t="s">
-        <v>45</v>
-      </c>
-      <c r="T100" t="s">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s">
-        <v>35</v>
-      </c>
-      <c r="X100">
+        <v>59</v>
+      </c>
+      <c r="P100" t="s">
+        <v>29</v>
+      </c>
+      <c r="W100" t="s">
+        <v>41</v>
+      </c>
+      <c r="X100" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB100">
         <v>6</v>
       </c>
     </row>
@@ -5099,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D101">
         <v>3</v>
@@ -5111,36 +5384,39 @@
         <v>-22</v>
       </c>
       <c r="G101" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J101">
         <v>5</v>
       </c>
       <c r="K101" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M101" t="s">
-        <v>52</v>
-      </c>
-      <c r="R101" t="s">
-        <v>35</v>
-      </c>
-      <c r="S101" t="s">
-        <v>45</v>
-      </c>
-      <c r="T101" t="s">
-        <v>53</v>
-      </c>
-      <c r="U101" t="s">
-        <v>36</v>
-      </c>
-      <c r="X101">
+        <v>59</v>
+      </c>
+      <c r="P101" t="s">
+        <v>29</v>
+      </c>
+      <c r="W101" t="s">
+        <v>40</v>
+      </c>
+      <c r="X101" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB101">
         <v>6</v>
       </c>
     </row>
@@ -5152,7 +5428,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D102">
         <v>4</v>
@@ -5164,24 +5440,24 @@
         <v>-27</v>
       </c>
       <c r="G102" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H102" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I102" t="s">
-        <v>91</v>
-      </c>
-      <c r="P102">
+        <v>101</v>
+      </c>
+      <c r="U102">
         <v>36</v>
       </c>
-      <c r="R102" t="s">
-        <v>36</v>
-      </c>
-      <c r="U102" t="s">
-        <v>36</v>
-      </c>
-      <c r="X102">
+      <c r="W102" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB102">
         <v>6</v>
       </c>
     </row>
@@ -5193,7 +5469,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -5205,19 +5481,19 @@
         <v>33</v>
       </c>
       <c r="G103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N103">
         <v>3</v>
@@ -5225,19 +5501,22 @@
       <c r="O103">
         <v>3</v>
       </c>
-      <c r="R103" t="s">
-        <v>35</v>
-      </c>
-      <c r="S103" t="s">
-        <v>45</v>
-      </c>
-      <c r="T103" t="s">
-        <v>89</v>
-      </c>
-      <c r="U103" t="s">
-        <v>36</v>
-      </c>
-      <c r="X103">
+      <c r="P103" t="s">
+        <v>57</v>
+      </c>
+      <c r="W103" t="s">
+        <v>40</v>
+      </c>
+      <c r="X103" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB103">
         <v>8</v>
       </c>
     </row>
@@ -5249,7 +5528,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5261,36 +5540,39 @@
         <v>33</v>
       </c>
       <c r="G104" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J104">
         <v>-5</v>
       </c>
       <c r="K104" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M104" t="s">
-        <v>58</v>
-      </c>
-      <c r="R104" t="s">
-        <v>35</v>
-      </c>
-      <c r="S104" t="s">
-        <v>83</v>
-      </c>
-      <c r="T104" t="s">
-        <v>60</v>
-      </c>
-      <c r="U104" t="s">
-        <v>36</v>
-      </c>
-      <c r="X104">
+        <v>65</v>
+      </c>
+      <c r="P104" t="s">
+        <v>57</v>
+      </c>
+      <c r="W104" t="s">
+        <v>40</v>
+      </c>
+      <c r="X104" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -5302,7 +5584,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5314,36 +5596,39 @@
         <v>38</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J105">
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M105" t="s">
-        <v>67</v>
-      </c>
-      <c r="R105" t="s">
-        <v>35</v>
-      </c>
-      <c r="S105" t="s">
-        <v>55</v>
-      </c>
-      <c r="T105" t="s">
-        <v>79</v>
-      </c>
-      <c r="U105" t="s">
-        <v>35</v>
-      </c>
-      <c r="X105">
+        <v>76</v>
+      </c>
+      <c r="P105" t="s">
+        <v>57</v>
+      </c>
+      <c r="W105" t="s">
+        <v>40</v>
+      </c>
+      <c r="X105" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -5355,7 +5640,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -5367,39 +5652,42 @@
         <v>36</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I106" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J106">
         <v>-1</v>
       </c>
       <c r="K106" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M106" t="s">
-        <v>50</v>
-      </c>
-      <c r="R106" t="s">
-        <v>35</v>
-      </c>
-      <c r="S106" t="s">
-        <v>55</v>
-      </c>
-      <c r="T106" t="s">
-        <v>60</v>
-      </c>
-      <c r="U106" t="s">
-        <v>36</v>
-      </c>
-      <c r="V106" t="s">
-        <v>36</v>
-      </c>
-      <c r="X106">
+        <v>56</v>
+      </c>
+      <c r="P106" t="s">
+        <v>57</v>
+      </c>
+      <c r="W106" t="s">
+        <v>40</v>
+      </c>
+      <c r="X106" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -5411,7 +5699,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D107">
         <v>4</v>
@@ -5423,15 +5711,15 @@
         <v>37</v>
       </c>
       <c r="G107" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H107" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I107" t="s">
-        <v>93</v>
-      </c>
-      <c r="X107">
+        <v>103</v>
+      </c>
+      <c r="AB107">
         <v>8</v>
       </c>
     </row>
@@ -5443,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5455,30 +5743,33 @@
         <v>-20</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J108">
         <v>-5</v>
       </c>
       <c r="K108" t="s">
-        <v>32</v>
-      </c>
-      <c r="R108" t="s">
         <v>36</v>
       </c>
-      <c r="S108" t="s">
-        <v>65</v>
-      </c>
-      <c r="U108" t="s">
-        <v>35</v>
-      </c>
-      <c r="X108">
+      <c r="P108" t="s">
+        <v>44</v>
+      </c>
+      <c r="W108" t="s">
+        <v>41</v>
+      </c>
+      <c r="X108" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB108">
         <v>7</v>
       </c>
     </row>
@@ -5490,7 +5781,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5502,30 +5793,33 @@
         <v>-15</v>
       </c>
       <c r="G109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J109">
         <v>4</v>
       </c>
       <c r="K109" t="s">
-        <v>32</v>
-      </c>
-      <c r="R109" t="s">
         <v>36</v>
       </c>
-      <c r="S109" t="s">
-        <v>39</v>
-      </c>
-      <c r="U109" t="s">
-        <v>35</v>
-      </c>
-      <c r="X109">
+      <c r="P109" t="s">
+        <v>29</v>
+      </c>
+      <c r="W109" t="s">
+        <v>41</v>
+      </c>
+      <c r="X109" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB109">
         <v>7</v>
       </c>
     </row>
@@ -5537,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5549,30 +5843,33 @@
         <v>-19</v>
       </c>
       <c r="G110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H110" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I110" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J110">
         <v>12</v>
       </c>
       <c r="K110" t="s">
-        <v>44</v>
-      </c>
-      <c r="R110" t="s">
-        <v>33</v>
-      </c>
-      <c r="S110" t="s">
-        <v>34</v>
-      </c>
-      <c r="U110" t="s">
-        <v>35</v>
-      </c>
-      <c r="X110">
+        <v>50</v>
+      </c>
+      <c r="P110" t="s">
+        <v>37</v>
+      </c>
+      <c r="W110" t="s">
+        <v>38</v>
+      </c>
+      <c r="X110" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110">
         <v>7</v>
       </c>
     </row>
@@ -5584,7 +5881,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5596,30 +5893,33 @@
         <v>-31</v>
       </c>
       <c r="G111" t="s">
+        <v>40</v>
+      </c>
+      <c r="H111" t="s">
+        <v>34</v>
+      </c>
+      <c r="I111" t="s">
         <v>35</v>
       </c>
-      <c r="H111" t="s">
-        <v>30</v>
-      </c>
-      <c r="I111" t="s">
-        <v>31</v>
-      </c>
       <c r="J111">
         <v>3</v>
       </c>
       <c r="K111" t="s">
-        <v>32</v>
-      </c>
-      <c r="R111" t="s">
-        <v>33</v>
-      </c>
-      <c r="S111" t="s">
-        <v>34</v>
-      </c>
-      <c r="U111" t="s">
-        <v>35</v>
-      </c>
-      <c r="X111">
+        <v>36</v>
+      </c>
+      <c r="P111" t="s">
+        <v>37</v>
+      </c>
+      <c r="W111" t="s">
+        <v>38</v>
+      </c>
+      <c r="X111" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB111">
         <v>7</v>
       </c>
     </row>
@@ -5631,7 +5931,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -5643,30 +5943,33 @@
         <v>-34</v>
       </c>
       <c r="G112" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H112" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I112" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>32</v>
-      </c>
-      <c r="R112" t="s">
         <v>36</v>
       </c>
-      <c r="S112" t="s">
-        <v>39</v>
-      </c>
-      <c r="U112" t="s">
-        <v>35</v>
-      </c>
-      <c r="X112">
+      <c r="P112" t="s">
+        <v>104</v>
+      </c>
+      <c r="W112" t="s">
+        <v>41</v>
+      </c>
+      <c r="X112" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112">
         <v>7</v>
       </c>
     </row>
@@ -5678,7 +5981,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -5690,30 +5993,33 @@
         <v>-34</v>
       </c>
       <c r="G113" t="s">
+        <v>40</v>
+      </c>
+      <c r="H113" t="s">
+        <v>34</v>
+      </c>
+      <c r="I113" t="s">
         <v>35</v>
-      </c>
-      <c r="H113" t="s">
-        <v>30</v>
-      </c>
-      <c r="I113" t="s">
-        <v>31</v>
       </c>
       <c r="J113">
         <v>8</v>
       </c>
       <c r="K113" t="s">
-        <v>44</v>
-      </c>
-      <c r="R113" t="s">
-        <v>36</v>
-      </c>
-      <c r="S113" t="s">
-        <v>39</v>
-      </c>
-      <c r="U113" t="s">
-        <v>35</v>
-      </c>
-      <c r="X113">
+        <v>50</v>
+      </c>
+      <c r="P113" t="s">
+        <v>57</v>
+      </c>
+      <c r="W113" t="s">
+        <v>41</v>
+      </c>
+      <c r="X113" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB113">
         <v>7</v>
       </c>
     </row>
@@ -5725,7 +6031,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5737,30 +6043,33 @@
         <v>-42</v>
       </c>
       <c r="G114" t="s">
+        <v>40</v>
+      </c>
+      <c r="H114" t="s">
+        <v>34</v>
+      </c>
+      <c r="I114" t="s">
         <v>35</v>
       </c>
-      <c r="H114" t="s">
-        <v>30</v>
-      </c>
-      <c r="I114" t="s">
-        <v>31</v>
-      </c>
       <c r="J114">
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>32</v>
-      </c>
-      <c r="R114" t="s">
         <v>36</v>
       </c>
-      <c r="S114" t="s">
-        <v>39</v>
-      </c>
-      <c r="U114" t="s">
-        <v>35</v>
-      </c>
-      <c r="X114">
+      <c r="P114" t="s">
+        <v>44</v>
+      </c>
+      <c r="W114" t="s">
+        <v>41</v>
+      </c>
+      <c r="X114" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114">
         <v>7</v>
       </c>
     </row>
@@ -5772,7 +6081,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -5784,30 +6093,33 @@
         <v>-44</v>
       </c>
       <c r="G115" t="s">
+        <v>40</v>
+      </c>
+      <c r="H115" t="s">
+        <v>34</v>
+      </c>
+      <c r="I115" t="s">
         <v>35</v>
-      </c>
-      <c r="H115" t="s">
-        <v>30</v>
-      </c>
-      <c r="I115" t="s">
-        <v>31</v>
       </c>
       <c r="J115">
         <v>33</v>
       </c>
       <c r="K115" t="s">
-        <v>44</v>
-      </c>
-      <c r="R115" t="s">
-        <v>36</v>
-      </c>
-      <c r="S115" t="s">
-        <v>65</v>
-      </c>
-      <c r="U115" t="s">
-        <v>36</v>
-      </c>
-      <c r="X115">
+        <v>50</v>
+      </c>
+      <c r="P115" t="s">
+        <v>29</v>
+      </c>
+      <c r="W115" t="s">
+        <v>41</v>
+      </c>
+      <c r="X115" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB115">
         <v>7</v>
       </c>
     </row>
@@ -5819,7 +6131,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -5831,30 +6143,33 @@
         <v>23</v>
       </c>
       <c r="G116" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H116" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I116" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J116">
         <v>5</v>
       </c>
       <c r="K116" t="s">
-        <v>44</v>
-      </c>
-      <c r="R116" t="s">
-        <v>36</v>
-      </c>
-      <c r="S116" t="s">
-        <v>85</v>
-      </c>
-      <c r="U116" t="s">
-        <v>35</v>
-      </c>
-      <c r="X116">
+        <v>50</v>
+      </c>
+      <c r="P116" t="s">
+        <v>57</v>
+      </c>
+      <c r="W116" t="s">
+        <v>41</v>
+      </c>
+      <c r="X116" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB116">
         <v>7</v>
       </c>
     </row>
@@ -5866,7 +6181,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -5878,30 +6193,33 @@
         <v>18</v>
       </c>
       <c r="G117" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I117" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>32</v>
-      </c>
-      <c r="R117" t="s">
         <v>36</v>
       </c>
-      <c r="S117" t="s">
-        <v>85</v>
-      </c>
-      <c r="U117" t="s">
-        <v>35</v>
-      </c>
-      <c r="X117">
+      <c r="P117" t="s">
+        <v>57</v>
+      </c>
+      <c r="W117" t="s">
+        <v>41</v>
+      </c>
+      <c r="X117" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB117">
         <v>7</v>
       </c>
     </row>
@@ -5913,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -5925,30 +6243,33 @@
         <v>18</v>
       </c>
       <c r="G118" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H118" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I118" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J118">
         <v>18</v>
       </c>
       <c r="K118" t="s">
-        <v>44</v>
-      </c>
-      <c r="R118" t="s">
-        <v>35</v>
-      </c>
-      <c r="S118" t="s">
-        <v>39</v>
-      </c>
-      <c r="U118" t="s">
-        <v>36</v>
-      </c>
-      <c r="X118">
+        <v>50</v>
+      </c>
+      <c r="P118" t="s">
+        <v>29</v>
+      </c>
+      <c r="W118" t="s">
+        <v>40</v>
+      </c>
+      <c r="X118" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB118">
         <v>7</v>
       </c>
     </row>
@@ -5960,21 +6281,21 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F119">
         <v>3</v>
       </c>
       <c r="G119" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H119" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="I119" t="s">
-        <v>62</v>
-      </c>
-      <c r="X119">
+        <v>70</v>
+      </c>
+      <c r="AB119">
         <v>7</v>
       </c>
     </row>
@@ -5986,24 +6307,24 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F120">
         <v>-40</v>
       </c>
       <c r="G120" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H120" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I120" t="s">
-        <v>84</v>
-      </c>
-      <c r="P120">
+        <v>94</v>
+      </c>
+      <c r="U120">
         <v>50</v>
       </c>
-      <c r="Q120">
+      <c r="V120">
         <v>18</v>
       </c>
     </row>
@@ -6015,7 +6336,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6027,36 +6348,39 @@
         <v>-44</v>
       </c>
       <c r="G121" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J121">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M121" t="s">
-        <v>67</v>
-      </c>
-      <c r="R121" t="s">
-        <v>35</v>
-      </c>
-      <c r="S121" t="s">
-        <v>45</v>
-      </c>
-      <c r="T121" t="s">
-        <v>53</v>
-      </c>
-      <c r="U121" t="s">
-        <v>36</v>
-      </c>
-      <c r="X121">
+        <v>76</v>
+      </c>
+      <c r="P121" t="s">
+        <v>29</v>
+      </c>
+      <c r="W121" t="s">
+        <v>40</v>
+      </c>
+      <c r="X121" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB121">
         <v>9</v>
       </c>
     </row>
@@ -6068,7 +6392,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6080,36 +6404,39 @@
         <v>-45</v>
       </c>
       <c r="G122" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H122" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J122">
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M122" t="s">
-        <v>52</v>
-      </c>
-      <c r="R122" t="s">
-        <v>36</v>
-      </c>
-      <c r="S122" t="s">
-        <v>71</v>
-      </c>
-      <c r="T122" t="s">
-        <v>56</v>
-      </c>
-      <c r="U122" t="s">
-        <v>36</v>
-      </c>
-      <c r="X122">
+        <v>59</v>
+      </c>
+      <c r="P122" t="s">
+        <v>29</v>
+      </c>
+      <c r="W122" t="s">
+        <v>41</v>
+      </c>
+      <c r="X122" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB122">
         <v>9</v>
       </c>
     </row>
@@ -6121,7 +6448,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -6133,36 +6460,39 @@
         <v>-47</v>
       </c>
       <c r="G123" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H123" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I123" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M123" t="s">
-        <v>52</v>
-      </c>
-      <c r="R123" t="s">
-        <v>35</v>
-      </c>
-      <c r="S123" t="s">
-        <v>45</v>
-      </c>
-      <c r="T123" t="s">
-        <v>56</v>
-      </c>
-      <c r="U123" t="s">
-        <v>35</v>
-      </c>
-      <c r="X123">
+        <v>59</v>
+      </c>
+      <c r="P123" t="s">
+        <v>29</v>
+      </c>
+      <c r="W123" t="s">
+        <v>40</v>
+      </c>
+      <c r="X123" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB123">
         <v>9</v>
       </c>
     </row>
